--- a/output/tables/rolling_dy_results.xlsx
+++ b/output/tables/rolling_dy_results.xlsx
@@ -456,7 +456,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>43252</v>
+        <v>43254</v>
       </c>
       <c r="B2" t="n">
         <v>44.84315957057574</v>
@@ -465,12 +465,12 @@
         <v>3.986221890980217</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>43259</v>
+        <v>43261</v>
       </c>
       <c r="B3" t="n">
         <v>46.40126375194029</v>
@@ -479,12 +479,12 @@
         <v>4.744666379627462</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>43266</v>
+        <v>43268</v>
       </c>
       <c r="B4" t="n">
         <v>46.38834146395442</v>
@@ -493,12 +493,12 @@
         <v>4.67906307515999</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>43273</v>
+        <v>43275</v>
       </c>
       <c r="B5" t="n">
         <v>48.1128209135578</v>
@@ -507,12 +507,12 @@
         <v>5.127269564533115</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="B6" t="n">
         <v>49.12400013413724</v>
@@ -521,12 +521,12 @@
         <v>2.90262931339742</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>43287</v>
+        <v>43289</v>
       </c>
       <c r="B7" t="n">
         <v>48.67701271308596</v>
@@ -535,12 +535,12 @@
         <v>2.639640166155562</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>43294</v>
+        <v>43296</v>
       </c>
       <c r="B8" t="n">
         <v>48.50243783026335</v>
@@ -549,12 +549,12 @@
         <v>2.808456502430647</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>43301</v>
+        <v>43303</v>
       </c>
       <c r="B9" t="n">
         <v>49.1843521749347</v>
@@ -563,12 +563,12 @@
         <v>2.826949126302219</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>43308</v>
+        <v>43310</v>
       </c>
       <c r="B10" t="n">
         <v>49.58362063709027</v>
@@ -577,12 +577,12 @@
         <v>4.664011486568887</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>43315</v>
+        <v>43317</v>
       </c>
       <c r="B11" t="n">
         <v>49.84000145842018</v>
@@ -591,12 +591,12 @@
         <v>4.517575222311824</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>43322</v>
+        <v>43324</v>
       </c>
       <c r="B12" t="n">
         <v>48.46929366212029</v>
@@ -605,12 +605,12 @@
         <v>2.952558078948934</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>43329</v>
+        <v>43331</v>
       </c>
       <c r="B13" t="n">
         <v>47.87576355435334</v>
@@ -619,12 +619,12 @@
         <v>2.920588576441693</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>43336</v>
+        <v>43338</v>
       </c>
       <c r="B14" t="n">
         <v>47.51196291125027</v>
@@ -633,12 +633,12 @@
         <v>2.826506661005751</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>43343</v>
+        <v>43345</v>
       </c>
       <c r="B15" t="n">
         <v>47.5361978544625</v>
@@ -647,12 +647,12 @@
         <v>3.025865863701899</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>43350</v>
+        <v>43352</v>
       </c>
       <c r="B16" t="n">
         <v>47.6481998386889</v>
@@ -661,12 +661,12 @@
         <v>3.37791678656523</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>43357</v>
+        <v>43359</v>
       </c>
       <c r="B17" t="n">
         <v>47.66216188163704</v>
@@ -675,12 +675,12 @@
         <v>3.419765476255097</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>43364</v>
+        <v>43366</v>
       </c>
       <c r="B18" t="n">
         <v>49.04817837734666</v>
@@ -689,12 +689,12 @@
         <v>3.437575508000141</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>43371</v>
+        <v>43373</v>
       </c>
       <c r="B19" t="n">
         <v>49.00355726333346</v>
@@ -703,12 +703,12 @@
         <v>3.185401392021154</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>43378</v>
+        <v>43380</v>
       </c>
       <c r="B20" t="n">
         <v>49.14578694297174</v>
@@ -717,12 +717,12 @@
         <v>3.038091199169494</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>43385</v>
+        <v>43387</v>
       </c>
       <c r="B21" t="n">
         <v>49.73248182801047</v>
@@ -731,12 +731,12 @@
         <v>3.041895797482496</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>43392</v>
+        <v>43394</v>
       </c>
       <c r="B22" t="n">
         <v>49.97271665441794</v>
@@ -745,12 +745,12 @@
         <v>3.091773744480961</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>43399</v>
+        <v>43401</v>
       </c>
       <c r="B23" t="n">
         <v>50.99039193233659</v>
@@ -759,12 +759,12 @@
         <v>2.971792144435233</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>43406</v>
+        <v>43408</v>
       </c>
       <c r="B24" t="n">
         <v>51.18584301047866</v>
@@ -773,12 +773,12 @@
         <v>2.759677970589224</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>43413</v>
+        <v>43415</v>
       </c>
       <c r="B25" t="n">
         <v>50.52056018949535</v>
@@ -787,12 +787,12 @@
         <v>2.708458908459386</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>43420</v>
+        <v>43422</v>
       </c>
       <c r="B26" t="n">
         <v>50.82587297429284</v>
@@ -801,12 +801,12 @@
         <v>2.334939258995822</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>43427</v>
+        <v>43429</v>
       </c>
       <c r="B27" t="n">
         <v>52.47763781740238</v>
@@ -815,12 +815,12 @@
         <v>1.852678897551119</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>43434</v>
+        <v>43436</v>
       </c>
       <c r="B28" t="n">
         <v>52.76988650030548</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>43441</v>
+        <v>43443</v>
       </c>
       <c r="B29" t="n">
         <v>52.69686861612468</v>
@@ -848,7 +848,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>43448</v>
+        <v>43450</v>
       </c>
       <c r="B30" t="n">
         <v>53.19575387948345</v>
@@ -862,7 +862,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>43455</v>
+        <v>43457</v>
       </c>
       <c r="B31" t="n">
         <v>52.23073721784242</v>
@@ -876,7 +876,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>43462</v>
+        <v>43464</v>
       </c>
       <c r="B32" t="n">
         <v>52.17347245647996</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>43469</v>
+        <v>43471</v>
       </c>
       <c r="B33" t="n">
         <v>52.59869113986448</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>43476</v>
+        <v>43478</v>
       </c>
       <c r="B34" t="n">
         <v>52.04850071535011</v>
@@ -918,7 +918,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>43483</v>
+        <v>43485</v>
       </c>
       <c r="B35" t="n">
         <v>51.65390179691081</v>
@@ -932,7 +932,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>43490</v>
+        <v>43492</v>
       </c>
       <c r="B36" t="n">
         <v>51.24095663358884</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>43497</v>
+        <v>43499</v>
       </c>
       <c r="B37" t="n">
         <v>51.55915707098473</v>
@@ -960,7 +960,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>43504</v>
+        <v>43506</v>
       </c>
       <c r="B38" t="n">
         <v>51.167993954096</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>43511</v>
+        <v>43513</v>
       </c>
       <c r="B39" t="n">
         <v>51.69197238659404</v>
@@ -988,7 +988,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>43518</v>
+        <v>43520</v>
       </c>
       <c r="B40" t="n">
         <v>51.27240973589232</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>43525</v>
+        <v>43527</v>
       </c>
       <c r="B41" t="n">
         <v>51.41301782133573</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>43532</v>
+        <v>43534</v>
       </c>
       <c r="B42" t="n">
         <v>51.39319157636631</v>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>43539</v>
+        <v>43541</v>
       </c>
       <c r="B43" t="n">
         <v>50.81742569213397</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>43546</v>
+        <v>43548</v>
       </c>
       <c r="B44" t="n">
         <v>50.95452666315031</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>43553</v>
+        <v>43555</v>
       </c>
       <c r="B45" t="n">
         <v>49.42015944652024</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>43560</v>
+        <v>43562</v>
       </c>
       <c r="B46" t="n">
         <v>48.96316653876704</v>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>43567</v>
+        <v>43569</v>
       </c>
       <c r="B47" t="n">
         <v>47.90377807176763</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>43574</v>
+        <v>43576</v>
       </c>
       <c r="B48" t="n">
         <v>48.31612090186235</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>43581</v>
+        <v>43583</v>
       </c>
       <c r="B49" t="n">
         <v>48.53573524095768</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>43588</v>
+        <v>43590</v>
       </c>
       <c r="B50" t="n">
         <v>49.01186260135434</v>
@@ -1142,7 +1142,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>43595</v>
+        <v>43597</v>
       </c>
       <c r="B51" t="n">
         <v>49.19560507902005</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>43602</v>
+        <v>43604</v>
       </c>
       <c r="B52" t="n">
         <v>49.27809618036965</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>43609</v>
+        <v>43611</v>
       </c>
       <c r="B53" t="n">
         <v>48.82774020711998</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>43616</v>
+        <v>43618</v>
       </c>
       <c r="B54" t="n">
         <v>46.36359010919455</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>43623</v>
+        <v>43625</v>
       </c>
       <c r="B55" t="n">
         <v>47.5627774527612</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>43630</v>
+        <v>43632</v>
       </c>
       <c r="B56" t="n">
         <v>46.74677326071525</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>43637</v>
+        <v>43639</v>
       </c>
       <c r="B57" t="n">
         <v>46.94867720170225</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>43644</v>
+        <v>43646</v>
       </c>
       <c r="B58" t="n">
         <v>47.94816662345397</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>43651</v>
+        <v>43653</v>
       </c>
       <c r="B59" t="n">
         <v>47.64565271149994</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>43658</v>
+        <v>43660</v>
       </c>
       <c r="B60" t="n">
         <v>56.89407473858523</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>43665</v>
+        <v>43667</v>
       </c>
       <c r="B61" t="n">
         <v>48.08667373561917</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>43672</v>
+        <v>43674</v>
       </c>
       <c r="B62" t="n">
         <v>48.37226843860111</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>43679</v>
+        <v>43681</v>
       </c>
       <c r="B63" t="n">
         <v>59.4844774122864</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>43686</v>
+        <v>43688</v>
       </c>
       <c r="B64" t="n">
         <v>59.40911319306027</v>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>43693</v>
+        <v>43695</v>
       </c>
       <c r="B65" t="n">
         <v>49.22995749042104</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>43700</v>
+        <v>43702</v>
       </c>
       <c r="B66" t="n">
         <v>60.64432107733947</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>43707</v>
+        <v>43709</v>
       </c>
       <c r="B67" t="n">
         <v>49.45103278722829</v>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>43714</v>
+        <v>43716</v>
       </c>
       <c r="B68" t="n">
         <v>49.960015017643</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>43721</v>
+        <v>43723</v>
       </c>
       <c r="B69" t="n">
         <v>53.25151805216021</v>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>43728</v>
+        <v>43730</v>
       </c>
       <c r="B70" t="n">
         <v>64.14557096573888</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>43735</v>
+        <v>43737</v>
       </c>
       <c r="B71" t="n">
         <v>77.84653814259562</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>43742</v>
+        <v>43744</v>
       </c>
       <c r="B72" t="n">
         <v>69.67551873890189</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>43749</v>
+        <v>43751</v>
       </c>
       <c r="B73" t="n">
         <v>69.21489280956179</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>43756</v>
+        <v>43758</v>
       </c>
       <c r="B74" t="n">
         <v>69.22390675142361</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>43763</v>
+        <v>43765</v>
       </c>
       <c r="B75" t="n">
         <v>69.47415988895833</v>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>43770</v>
+        <v>43772</v>
       </c>
       <c r="B76" t="n">
         <v>68.92154522779551</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>43777</v>
+        <v>43779</v>
       </c>
       <c r="B77" t="n">
         <v>68.22800828057957</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>43784</v>
+        <v>43786</v>
       </c>
       <c r="B78" t="n">
         <v>68.96907654579707</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>43791</v>
+        <v>43793</v>
       </c>
       <c r="B79" t="n">
         <v>68.82319314433128</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>43798</v>
+        <v>43800</v>
       </c>
       <c r="B80" t="n">
         <v>68.97599356422462</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>43805</v>
+        <v>43807</v>
       </c>
       <c r="B81" t="n">
         <v>69.10809675824306</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>43812</v>
+        <v>43814</v>
       </c>
       <c r="B82" t="n">
         <v>69.62493683107692</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>43819</v>
+        <v>43821</v>
       </c>
       <c r="B83" t="n">
         <v>69.36099335688738</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>43826</v>
+        <v>43828</v>
       </c>
       <c r="B84" t="n">
         <v>68.51466327143332</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>43833</v>
+        <v>43835</v>
       </c>
       <c r="B85" t="n">
         <v>69.19079855519119</v>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>43840</v>
+        <v>43842</v>
       </c>
       <c r="B86" t="n">
         <v>68.44265731419166</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>43847</v>
+        <v>43849</v>
       </c>
       <c r="B87" t="n">
         <v>68.15923772760075</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>43854</v>
+        <v>43856</v>
       </c>
       <c r="B88" t="n">
         <v>68.48821960318776</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>43861</v>
+        <v>43863</v>
       </c>
       <c r="B89" t="n">
         <v>70.35078436963494</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>43868</v>
+        <v>43870</v>
       </c>
       <c r="B90" t="n">
         <v>68.36970151886803</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>43875</v>
+        <v>43877</v>
       </c>
       <c r="B91" t="n">
         <v>73.29389506823033</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>43882</v>
+        <v>43884</v>
       </c>
       <c r="B92" t="n">
         <v>73.61845754359986</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>43889</v>
+        <v>43891</v>
       </c>
       <c r="B93" t="n">
         <v>69.83031853928969</v>
@@ -1744,7 +1744,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>43896</v>
+        <v>43898</v>
       </c>
       <c r="B94" t="n">
         <v>68.10925119391379</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>43903</v>
+        <v>43905</v>
       </c>
       <c r="B95" t="n">
         <v>68.63943489696747</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>43910</v>
+        <v>43912</v>
       </c>
       <c r="B96" t="n">
         <v>69.32509194835872</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>43917</v>
+        <v>43919</v>
       </c>
       <c r="B97" t="n">
         <v>70.99591212539424</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>43924</v>
+        <v>43926</v>
       </c>
       <c r="B98" t="n">
         <v>71.2817234379883</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>43931</v>
+        <v>43933</v>
       </c>
       <c r="B99" t="n">
         <v>71.65928871763786</v>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>43938</v>
+        <v>43940</v>
       </c>
       <c r="B100" t="n">
         <v>71.60232466446725</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>43945</v>
+        <v>43947</v>
       </c>
       <c r="B101" t="n">
         <v>68.11976043269628</v>
@@ -1856,7 +1856,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>43952</v>
+        <v>43954</v>
       </c>
       <c r="B102" t="n">
         <v>68.04205576175153</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>43959</v>
+        <v>43961</v>
       </c>
       <c r="B103" t="n">
         <v>70.74052335752515</v>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>43966</v>
+        <v>43968</v>
       </c>
       <c r="B104" t="n">
         <v>72.12954560819769</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>43973</v>
+        <v>43975</v>
       </c>
       <c r="B105" t="n">
         <v>70.71010038799743</v>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>43980</v>
+        <v>43982</v>
       </c>
       <c r="B106" t="n">
         <v>67.26329696369093</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>43987</v>
+        <v>43989</v>
       </c>
       <c r="B107" t="n">
         <v>71.1518215599496</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>43994</v>
+        <v>43996</v>
       </c>
       <c r="B108" t="n">
         <v>71.62394875875789</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>44001</v>
+        <v>44003</v>
       </c>
       <c r="B109" t="n">
         <v>74.7859650122849</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>44008</v>
+        <v>44010</v>
       </c>
       <c r="B110" t="n">
         <v>69.12417124086784</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>44015</v>
+        <v>44017</v>
       </c>
       <c r="B111" t="n">
         <v>68.90901934085032</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>44022</v>
+        <v>44024</v>
       </c>
       <c r="B112" t="n">
         <v>68.65118177808326</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>44029</v>
+        <v>44031</v>
       </c>
       <c r="B113" t="n">
         <v>68.1130634920065</v>
@@ -2019,12 +2019,12 @@
         <v>10.54243345992156</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>44036</v>
+        <v>44038</v>
       </c>
       <c r="B114" t="n">
         <v>68.51885188681577</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>44043</v>
+        <v>44045</v>
       </c>
       <c r="B115" t="n">
         <v>71.87578620481155</v>
@@ -2052,7 +2052,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>44050</v>
+        <v>44052</v>
       </c>
       <c r="B116" t="n">
         <v>69.78520157764025</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>44057</v>
+        <v>44059</v>
       </c>
       <c r="B117" t="n">
         <v>66.89965476701417</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>44064</v>
+        <v>44066</v>
       </c>
       <c r="B118" t="n">
         <v>66.21115743626309</v>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>44071</v>
+        <v>44073</v>
       </c>
       <c r="B119" t="n">
         <v>60.66866227000022</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>44078</v>
+        <v>44080</v>
       </c>
       <c r="B120" t="n">
         <v>58.63235816445948</v>
@@ -2122,7 +2122,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>44085</v>
+        <v>44087</v>
       </c>
       <c r="B121" t="n">
         <v>57.80113453969899</v>
@@ -2136,7 +2136,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>44092</v>
+        <v>44094</v>
       </c>
       <c r="B122" t="n">
         <v>45.55852920825319</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>44099</v>
+        <v>44101</v>
       </c>
       <c r="B123" t="n">
         <v>45.61157626898211</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>44106</v>
+        <v>44108</v>
       </c>
       <c r="B124" t="n">
         <v>45.83725847334838</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>44113</v>
+        <v>44115</v>
       </c>
       <c r="B125" t="n">
         <v>45.79763980463407</v>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>44120</v>
+        <v>44122</v>
       </c>
       <c r="B126" t="n">
         <v>45.67561221889184</v>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>44127</v>
+        <v>44129</v>
       </c>
       <c r="B127" t="n">
         <v>46.18806668973013</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>44134</v>
+        <v>44136</v>
       </c>
       <c r="B128" t="n">
         <v>46.16580856091651</v>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>44141</v>
+        <v>44143</v>
       </c>
       <c r="B129" t="n">
         <v>44.33432590372473</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>44148</v>
+        <v>44150</v>
       </c>
       <c r="B130" t="n">
         <v>42.64004478017489</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>44155</v>
+        <v>44157</v>
       </c>
       <c r="B131" t="n">
         <v>43.34948044919346</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>44162</v>
+        <v>44164</v>
       </c>
       <c r="B132" t="n">
         <v>42.49594603334941</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>44169</v>
+        <v>44171</v>
       </c>
       <c r="B133" t="n">
         <v>43.83011465782937</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>44176</v>
+        <v>44178</v>
       </c>
       <c r="B134" t="n">
         <v>45.01362819281874</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>44183</v>
+        <v>44185</v>
       </c>
       <c r="B135" t="n">
         <v>45.03874931163569</v>
@@ -2332,7 +2332,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>44190</v>
+        <v>44192</v>
       </c>
       <c r="B136" t="n">
         <v>44.8466721779125</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>44197</v>
+        <v>44199</v>
       </c>
       <c r="B137" t="n">
         <v>43.71925660659534</v>
@@ -2360,7 +2360,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>44204</v>
+        <v>44206</v>
       </c>
       <c r="B138" t="n">
         <v>43.83747068310324</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>44211</v>
+        <v>44213</v>
       </c>
       <c r="B139" t="n">
         <v>43.64836044172184</v>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>44218</v>
+        <v>44220</v>
       </c>
       <c r="B140" t="n">
         <v>43.7082569792821</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>44225</v>
+        <v>44227</v>
       </c>
       <c r="B141" t="n">
         <v>44.19629468697021</v>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>44232</v>
+        <v>44234</v>
       </c>
       <c r="B142" t="n">
         <v>43.55445045798538</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>44239</v>
+        <v>44241</v>
       </c>
       <c r="B143" t="n">
         <v>43.3989380932056</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>44246</v>
+        <v>44248</v>
       </c>
       <c r="B144" t="n">
         <v>42.15892612332724</v>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>44253</v>
+        <v>44255</v>
       </c>
       <c r="B145" t="n">
         <v>43.58431444769146</v>
@@ -2472,7 +2472,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>44260</v>
+        <v>44262</v>
       </c>
       <c r="B146" t="n">
         <v>56.90095747870546</v>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>44267</v>
+        <v>44269</v>
       </c>
       <c r="B147" t="n">
         <v>56.74017368137576</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>44274</v>
+        <v>44276</v>
       </c>
       <c r="B148" t="n">
         <v>56.71305409049125</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>44281</v>
+        <v>44283</v>
       </c>
       <c r="B149" t="n">
         <v>44.76127369758095</v>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>44288</v>
+        <v>44290</v>
       </c>
       <c r="B150" t="n">
         <v>44.43425157477884</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>44295</v>
+        <v>44297</v>
       </c>
       <c r="B151" t="n">
         <v>44.71097169223165</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>44302</v>
+        <v>44304</v>
       </c>
       <c r="B152" t="n">
         <v>44.69962130786497</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>44309</v>
+        <v>44311</v>
       </c>
       <c r="B153" t="n">
         <v>45.24078780372398</v>
@@ -2584,7 +2584,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>44316</v>
+        <v>44318</v>
       </c>
       <c r="B154" t="n">
         <v>43.89792995173406</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>44323</v>
+        <v>44325</v>
       </c>
       <c r="B155" t="n">
         <v>43.90341905655487</v>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>44330</v>
+        <v>44332</v>
       </c>
       <c r="B156" t="n">
         <v>44.63748202397556</v>
@@ -2626,7 +2626,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>44337</v>
+        <v>44339</v>
       </c>
       <c r="B157" t="n">
         <v>44.52455956417384</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>44344</v>
+        <v>44346</v>
       </c>
       <c r="B158" t="n">
         <v>43.79177020410773</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>44351</v>
+        <v>44353</v>
       </c>
       <c r="B159" t="n">
         <v>43.79695670038211</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>44358</v>
+        <v>44360</v>
       </c>
       <c r="B160" t="n">
         <v>44.47101115468941</v>
@@ -2682,7 +2682,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>44365</v>
+        <v>44367</v>
       </c>
       <c r="B161" t="n">
         <v>43.28051612511197</v>
@@ -2696,7 +2696,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>44372</v>
+        <v>44374</v>
       </c>
       <c r="B162" t="n">
         <v>43.46996123845963</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>44379</v>
+        <v>44381</v>
       </c>
       <c r="B163" t="n">
         <v>43.53460470022936</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>44386</v>
+        <v>44388</v>
       </c>
       <c r="B164" t="n">
         <v>43.28460032662452</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>44393</v>
+        <v>44395</v>
       </c>
       <c r="B165" t="n">
         <v>41.52815146459199</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>44400</v>
+        <v>44402</v>
       </c>
       <c r="B166" t="n">
         <v>41.83609318155632</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>44407</v>
+        <v>44409</v>
       </c>
       <c r="B167" t="n">
         <v>41.15723561069464</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>44414</v>
+        <v>44416</v>
       </c>
       <c r="B168" t="n">
         <v>44.28849529590832</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>44421</v>
+        <v>44423</v>
       </c>
       <c r="B169" t="n">
         <v>43.47145520380594</v>
@@ -2808,7 +2808,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>44428</v>
+        <v>44430</v>
       </c>
       <c r="B170" t="n">
         <v>43.574304279876</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>44435</v>
+        <v>44437</v>
       </c>
       <c r="B171" t="n">
         <v>43.67406091358171</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>44442</v>
+        <v>44444</v>
       </c>
       <c r="B172" t="n">
         <v>43.66137992085746</v>
@@ -2850,7 +2850,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>44449</v>
+        <v>44451</v>
       </c>
       <c r="B173" t="n">
         <v>43.28735787576977</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>44456</v>
+        <v>44458</v>
       </c>
       <c r="B174" t="n">
         <v>43.25929103620646</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>44463</v>
+        <v>44465</v>
       </c>
       <c r="B175" t="n">
         <v>43.11677915883276</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>44470</v>
+        <v>44472</v>
       </c>
       <c r="B176" t="n">
         <v>43.28960593555141</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>44477</v>
+        <v>44479</v>
       </c>
       <c r="B177" t="n">
         <v>43.77996347872266</v>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>44484</v>
+        <v>44486</v>
       </c>
       <c r="B178" t="n">
         <v>43.59965373314915</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>44491</v>
+        <v>44493</v>
       </c>
       <c r="B179" t="n">
         <v>43.27878782756103</v>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>44498</v>
+        <v>44500</v>
       </c>
       <c r="B180" t="n">
         <v>44.45325705292453</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>44505</v>
+        <v>44507</v>
       </c>
       <c r="B181" t="n">
         <v>44.06784231199794</v>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>44512</v>
+        <v>44514</v>
       </c>
       <c r="B182" t="n">
         <v>44.10847353198568</v>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>44519</v>
+        <v>44521</v>
       </c>
       <c r="B183" t="n">
         <v>44.46036009166416</v>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>44526</v>
+        <v>44528</v>
       </c>
       <c r="B184" t="n">
         <v>45.56562654098624</v>
@@ -3013,12 +3013,12 @@
         <v>4.898020445417184</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>44533</v>
+        <v>44535</v>
       </c>
       <c r="B185" t="n">
         <v>46.68216752806477</v>
@@ -3027,12 +3027,12 @@
         <v>5.630682790958424</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>44540</v>
+        <v>44542</v>
       </c>
       <c r="B186" t="n">
         <v>46.24778934105169</v>
@@ -3041,12 +3041,12 @@
         <v>5.527385453815601</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>44547</v>
+        <v>44549</v>
       </c>
       <c r="B187" t="n">
         <v>46.68653453917364</v>
@@ -3055,12 +3055,12 @@
         <v>5.327972187098617</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>44554</v>
+        <v>44556</v>
       </c>
       <c r="B188" t="n">
         <v>47.76073345949199</v>
@@ -3069,12 +3069,12 @@
         <v>5.668423086705728</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>44561</v>
+        <v>44563</v>
       </c>
       <c r="B189" t="n">
         <v>49.45369673309111</v>
@@ -3083,12 +3083,12 @@
         <v>8.306041812979576</v>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>44568</v>
+        <v>44570</v>
       </c>
       <c r="B190" t="n">
         <v>48.13866492016487</v>
@@ -3097,12 +3097,12 @@
         <v>7.016033726791388</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>44575</v>
+        <v>44577</v>
       </c>
       <c r="B191" t="n">
         <v>47.67057455254463</v>
@@ -3111,12 +3111,12 @@
         <v>6.37948106082086</v>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>44582</v>
+        <v>44584</v>
       </c>
       <c r="B192" t="n">
         <v>47.87374804649225</v>
@@ -3125,12 +3125,12 @@
         <v>6.121914988168655</v>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>44589</v>
+        <v>44591</v>
       </c>
       <c r="B193" t="n">
         <v>47.78361294123985</v>
@@ -3139,12 +3139,12 @@
         <v>5.858054460797173</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>44596</v>
+        <v>44598</v>
       </c>
       <c r="B194" t="n">
         <v>47.40737743693477</v>
@@ -3153,12 +3153,12 @@
         <v>5.573668888914858</v>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>44603</v>
+        <v>44605</v>
       </c>
       <c r="B195" t="n">
         <v>47.1575893556994</v>
@@ -3167,12 +3167,12 @@
         <v>5.425470092162612</v>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>44610</v>
+        <v>44612</v>
       </c>
       <c r="B196" t="n">
         <v>46.5419953670764</v>
@@ -3181,12 +3181,12 @@
         <v>5.338900869504201</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>44617</v>
+        <v>44619</v>
       </c>
       <c r="B197" t="n">
         <v>46.88795621972477</v>
@@ -3195,12 +3195,12 @@
         <v>5.721543999226414</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>44624</v>
+        <v>44626</v>
       </c>
       <c r="B198" t="n">
         <v>47.30036345005417</v>
@@ -3209,12 +3209,12 @@
         <v>5.573692703349126</v>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>44631</v>
+        <v>44633</v>
       </c>
       <c r="B199" t="n">
         <v>47.63149066439808</v>
@@ -3223,12 +3223,12 @@
         <v>5.940720589371833</v>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>44638</v>
+        <v>44640</v>
       </c>
       <c r="B200" t="n">
         <v>47.1540433819254</v>
@@ -3237,12 +3237,12 @@
         <v>5.15138291178179</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>44645</v>
+        <v>44647</v>
       </c>
       <c r="B201" t="n">
         <v>47.40831825780452</v>
@@ -3251,12 +3251,12 @@
         <v>5.501663763164514</v>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>44652</v>
+        <v>44654</v>
       </c>
       <c r="B202" t="n">
         <v>47.7426152960604</v>
@@ -3265,12 +3265,12 @@
         <v>6.233338489382094</v>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>44659</v>
+        <v>44661</v>
       </c>
       <c r="B203" t="n">
         <v>48.08197363720996</v>
@@ -3279,12 +3279,12 @@
         <v>6.8416021799956</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>44666</v>
+        <v>44668</v>
       </c>
       <c r="B204" t="n">
         <v>47.63158766354103</v>
@@ -3293,12 +3293,12 @@
         <v>6.517315372056437</v>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>44673</v>
+        <v>44675</v>
       </c>
       <c r="B205" t="n">
         <v>48.04147038127807</v>
@@ -3307,12 +3307,12 @@
         <v>6.396298848837113</v>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>44680</v>
+        <v>44682</v>
       </c>
       <c r="B206" t="n">
         <v>48.31029188908289</v>
@@ -3321,12 +3321,12 @@
         <v>6.546613063169805</v>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>44687</v>
+        <v>44689</v>
       </c>
       <c r="B207" t="n">
         <v>46.54879931380676</v>
@@ -3335,12 +3335,12 @@
         <v>6.536139681152452</v>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>44694</v>
+        <v>44696</v>
       </c>
       <c r="B208" t="n">
         <v>46.75195895437773</v>
@@ -3349,12 +3349,12 @@
         <v>6.652275083317985</v>
       </c>
       <c r="D208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>44701</v>
+        <v>44703</v>
       </c>
       <c r="B209" t="n">
         <v>46.91783726215656</v>
@@ -3363,12 +3363,12 @@
         <v>6.232221287932333</v>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>44708</v>
+        <v>44710</v>
       </c>
       <c r="B210" t="n">
         <v>46.53660485425531</v>
@@ -3377,12 +3377,12 @@
         <v>5.549921548041087</v>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>44715</v>
+        <v>44717</v>
       </c>
       <c r="B211" t="n">
         <v>46.60346815473141</v>
@@ -3391,12 +3391,12 @@
         <v>5.578675788406072</v>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>44722</v>
+        <v>44724</v>
       </c>
       <c r="B212" t="n">
         <v>46.50346022074837</v>
@@ -3405,12 +3405,12 @@
         <v>5.767311057450654</v>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>44729</v>
+        <v>44731</v>
       </c>
       <c r="B213" t="n">
         <v>46.53707921598892</v>
@@ -3419,12 +3419,12 @@
         <v>5.67538950526243</v>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>44736</v>
+        <v>44738</v>
       </c>
       <c r="B214" t="n">
         <v>46.36909685822869</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>44743</v>
+        <v>44745</v>
       </c>
       <c r="B215" t="n">
         <v>46.04966310923142</v>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>44750</v>
+        <v>44752</v>
       </c>
       <c r="B216" t="n">
         <v>45.91614317194342</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>44757</v>
+        <v>44759</v>
       </c>
       <c r="B217" t="n">
         <v>45.05991952721173</v>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>44764</v>
+        <v>44766</v>
       </c>
       <c r="B218" t="n">
         <v>45.41584317742902</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>44771</v>
+        <v>44773</v>
       </c>
       <c r="B219" t="n">
         <v>44.65723577029908</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>44778</v>
+        <v>44780</v>
       </c>
       <c r="B220" t="n">
         <v>44.70176686378834</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>44785</v>
+        <v>44787</v>
       </c>
       <c r="B221" t="n">
         <v>44.9352400779421</v>
@@ -3536,7 +3536,7 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>44792</v>
+        <v>44794</v>
       </c>
       <c r="B222" t="n">
         <v>44.4964596494688</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>44799</v>
+        <v>44801</v>
       </c>
       <c r="B223" t="n">
         <v>44.83517584937215</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>44806</v>
+        <v>44808</v>
       </c>
       <c r="B224" t="n">
         <v>44.63694042944697</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>44813</v>
+        <v>44815</v>
       </c>
       <c r="B225" t="n">
         <v>44.49796378135983</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>44820</v>
+        <v>44822</v>
       </c>
       <c r="B226" t="n">
         <v>44.54176453336328</v>
@@ -3606,7 +3606,7 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>44827</v>
+        <v>44829</v>
       </c>
       <c r="B227" t="n">
         <v>44.97011403699207</v>
@@ -3620,7 +3620,7 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>44834</v>
+        <v>44836</v>
       </c>
       <c r="B228" t="n">
         <v>43.07700801736704</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>44841</v>
+        <v>44843</v>
       </c>
       <c r="B229" t="n">
         <v>42.84922934062016</v>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>44848</v>
+        <v>44850</v>
       </c>
       <c r="B230" t="n">
         <v>41.99223355831197</v>
@@ -3662,7 +3662,7 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>44855</v>
+        <v>44857</v>
       </c>
       <c r="B231" t="n">
         <v>42.23203630210434</v>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>44862</v>
+        <v>44864</v>
       </c>
       <c r="B232" t="n">
         <v>42.30232621459808</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>44869</v>
+        <v>44871</v>
       </c>
       <c r="B233" t="n">
         <v>42.00239538844885</v>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>44876</v>
+        <v>44878</v>
       </c>
       <c r="B234" t="n">
         <v>41.99701684132638</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>44883</v>
+        <v>44885</v>
       </c>
       <c r="B235" t="n">
         <v>42.27881379725189</v>
@@ -3732,7 +3732,7 @@
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>44890</v>
+        <v>44892</v>
       </c>
       <c r="B236" t="n">
         <v>42.28529101082705</v>
@@ -3746,7 +3746,7 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>44897</v>
+        <v>44899</v>
       </c>
       <c r="B237" t="n">
         <v>42.75492778275834</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>44904</v>
+        <v>44906</v>
       </c>
       <c r="B238" t="n">
         <v>42.74957635992778</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>44911</v>
+        <v>44913</v>
       </c>
       <c r="B239" t="n">
         <v>42.98244397379935</v>
@@ -3788,7 +3788,7 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>44918</v>
+        <v>44920</v>
       </c>
       <c r="B240" t="n">
         <v>42.17867082587586</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>44925</v>
+        <v>44927</v>
       </c>
       <c r="B241" t="n">
         <v>42.21085877502213</v>
@@ -3816,7 +3816,7 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>44932</v>
+        <v>44934</v>
       </c>
       <c r="B242" t="n">
         <v>42.54877502795344</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>44939</v>
+        <v>44941</v>
       </c>
       <c r="B243" t="n">
         <v>42.47149721801934</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>44946</v>
+        <v>44948</v>
       </c>
       <c r="B244" t="n">
         <v>42.03987687351229</v>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>44953</v>
+        <v>44955</v>
       </c>
       <c r="B245" t="n">
         <v>42.2776614078325</v>
@@ -3872,7 +3872,7 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>44960</v>
+        <v>44962</v>
       </c>
       <c r="B246" t="n">
         <v>42.30762825932936</v>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>44967</v>
+        <v>44969</v>
       </c>
       <c r="B247" t="n">
         <v>43.26827309280534</v>
@@ -3900,7 +3900,7 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>44974</v>
+        <v>44976</v>
       </c>
       <c r="B248" t="n">
         <v>42.73489876921405</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>44981</v>
+        <v>44983</v>
       </c>
       <c r="B249" t="n">
         <v>41.84806960128871</v>
@@ -3928,7 +3928,7 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>44988</v>
+        <v>44990</v>
       </c>
       <c r="B250" t="n">
         <v>41.97049491001571</v>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>44995</v>
+        <v>44997</v>
       </c>
       <c r="B251" t="n">
         <v>41.77706200780528</v>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>45002</v>
+        <v>45004</v>
       </c>
       <c r="B252" t="n">
         <v>41.74937086755033</v>
@@ -3970,7 +3970,7 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>45009</v>
+        <v>45011</v>
       </c>
       <c r="B253" t="n">
         <v>41.54889910813059</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>45016</v>
+        <v>45018</v>
       </c>
       <c r="B254" t="n">
         <v>41.84494569858085</v>
@@ -3998,7 +3998,7 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>45023</v>
+        <v>45025</v>
       </c>
       <c r="B255" t="n">
         <v>42.61786941865331</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>45030</v>
+        <v>45032</v>
       </c>
       <c r="B256" t="n">
         <v>42.80235921464963</v>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>45037</v>
+        <v>45039</v>
       </c>
       <c r="B257" t="n">
         <v>43.18646537014812</v>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>45044</v>
+        <v>45046</v>
       </c>
       <c r="B258" t="n">
         <v>45.67366589101519</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>45051</v>
+        <v>45053</v>
       </c>
       <c r="B259" t="n">
         <v>45.65480360807512</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>45058</v>
+        <v>45060</v>
       </c>
       <c r="B260" t="n">
         <v>45.62914455292887</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>45065</v>
+        <v>45067</v>
       </c>
       <c r="B261" t="n">
         <v>44.85263408159017</v>
@@ -4096,7 +4096,7 @@
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>45072</v>
+        <v>45074</v>
       </c>
       <c r="B262" t="n">
         <v>45.53923863669505</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>45079</v>
+        <v>45081</v>
       </c>
       <c r="B263" t="n">
         <v>45.43947027962923</v>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>45086</v>
+        <v>45088</v>
       </c>
       <c r="B264" t="n">
         <v>45.87296412814734</v>
@@ -4138,7 +4138,7 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>45093</v>
+        <v>45095</v>
       </c>
       <c r="B265" t="n">
         <v>46.2074870738731</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>45100</v>
+        <v>45102</v>
       </c>
       <c r="B266" t="n">
         <v>46.48404374746608</v>
@@ -4166,7 +4166,7 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>45107</v>
+        <v>45109</v>
       </c>
       <c r="B267" t="n">
         <v>46.15679421373363</v>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>45114</v>
+        <v>45116</v>
       </c>
       <c r="B268" t="n">
         <v>46.294709497474</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>45121</v>
+        <v>45123</v>
       </c>
       <c r="B269" t="n">
         <v>45.88897974794526</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>45128</v>
+        <v>45130</v>
       </c>
       <c r="B270" t="n">
         <v>45.38101965863648</v>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>45135</v>
+        <v>45137</v>
       </c>
       <c r="B271" t="n">
         <v>45.32195525821382</v>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>45142</v>
+        <v>45144</v>
       </c>
       <c r="B272" t="n">
         <v>45.68018970064964</v>
@@ -4250,7 +4250,7 @@
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>45149</v>
+        <v>45151</v>
       </c>
       <c r="B273" t="n">
         <v>44.23419187948976</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>45156</v>
+        <v>45158</v>
       </c>
       <c r="B274" t="n">
         <v>43.80265101459094</v>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>45163</v>
+        <v>45165</v>
       </c>
       <c r="B275" t="n">
         <v>44.25203786341626</v>
@@ -4292,7 +4292,7 @@
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>45170</v>
+        <v>45172</v>
       </c>
       <c r="B276" t="n">
         <v>44.29639879718491</v>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>45177</v>
+        <v>45179</v>
       </c>
       <c r="B277" t="n">
         <v>44.26745777594528</v>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>45184</v>
+        <v>45186</v>
       </c>
       <c r="B278" t="n">
         <v>42.78085219013035</v>
@@ -4329,12 +4329,12 @@
         <v>1.600001889437241</v>
       </c>
       <c r="D278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>45191</v>
+        <v>45193</v>
       </c>
       <c r="B279" t="n">
         <v>42.77575304954746</v>
@@ -4343,12 +4343,12 @@
         <v>1.433223242937959</v>
       </c>
       <c r="D279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>45198</v>
+        <v>45200</v>
       </c>
       <c r="B280" t="n">
         <v>42.7960229587969</v>
@@ -4357,12 +4357,12 @@
         <v>1.608272000996635</v>
       </c>
       <c r="D280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>45205</v>
+        <v>45207</v>
       </c>
       <c r="B281" t="n">
         <v>42.89033746360929</v>
@@ -4371,12 +4371,12 @@
         <v>1.560548380006221</v>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>45212</v>
+        <v>45214</v>
       </c>
       <c r="B282" t="n">
         <v>43.32426804853966</v>
@@ -4385,12 +4385,12 @@
         <v>1.455599053640696</v>
       </c>
       <c r="D282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>45219</v>
+        <v>45221</v>
       </c>
       <c r="B283" t="n">
         <v>43.90978941737979</v>
@@ -4399,12 +4399,12 @@
         <v>1.65454593887044</v>
       </c>
       <c r="D283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>45226</v>
+        <v>45228</v>
       </c>
       <c r="B284" t="n">
         <v>42.11491183270771</v>
@@ -4413,12 +4413,12 @@
         <v>1.242845038176279</v>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
-        <v>45233</v>
+        <v>45235</v>
       </c>
       <c r="B285" t="n">
         <v>42.47865732500543</v>
@@ -4427,12 +4427,12 @@
         <v>1.331826047227619</v>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>45240</v>
+        <v>45242</v>
       </c>
       <c r="B286" t="n">
         <v>42.04552616372981</v>
@@ -4441,12 +4441,12 @@
         <v>1.395868009243358</v>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>45247</v>
+        <v>45249</v>
       </c>
       <c r="B287" t="n">
         <v>40.40260750295141</v>
@@ -4455,12 +4455,12 @@
         <v>1.640156588090561</v>
       </c>
       <c r="D287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="B288" t="n">
         <v>41.12635789372693</v>
@@ -4469,12 +4469,12 @@
         <v>2.233538809038504</v>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
-        <v>45261</v>
+        <v>45263</v>
       </c>
       <c r="B289" t="n">
         <v>41.56940169346981</v>
@@ -4483,12 +4483,12 @@
         <v>2.331961619248363</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
-        <v>45268</v>
+        <v>45270</v>
       </c>
       <c r="B290" t="n">
         <v>41.18658531346094</v>
@@ -4497,12 +4497,12 @@
         <v>2.120445574481684</v>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
-        <v>45275</v>
+        <v>45277</v>
       </c>
       <c r="B291" t="n">
         <v>40.79787819693296</v>
@@ -4511,12 +4511,12 @@
         <v>2.093908361750457</v>
       </c>
       <c r="D291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
-        <v>45282</v>
+        <v>45284</v>
       </c>
       <c r="B292" t="n">
         <v>42.01213896921676</v>
@@ -4525,12 +4525,12 @@
         <v>2.620975183762216</v>
       </c>
       <c r="D292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
-        <v>45289</v>
+        <v>45291</v>
       </c>
       <c r="B293" t="n">
         <v>42.6375902734434</v>
@@ -4539,12 +4539,12 @@
         <v>3.09840176436655</v>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
-        <v>45296</v>
+        <v>45298</v>
       </c>
       <c r="B294" t="n">
         <v>41.86212919163922</v>
@@ -4553,12 +4553,12 @@
         <v>2.94830958649357</v>
       </c>
       <c r="D294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
-        <v>45303</v>
+        <v>45305</v>
       </c>
       <c r="B295" t="n">
         <v>41.19432622204437</v>
@@ -4567,12 +4567,12 @@
         <v>2.775936179598136</v>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
-        <v>45310</v>
+        <v>45312</v>
       </c>
       <c r="B296" t="n">
         <v>40.39934428491393</v>
@@ -4581,12 +4581,12 @@
         <v>2.296743247635284</v>
       </c>
       <c r="D296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
-        <v>45317</v>
+        <v>45319</v>
       </c>
       <c r="B297" t="n">
         <v>40.0888916435706</v>
@@ -4595,12 +4595,12 @@
         <v>2.102561191738447</v>
       </c>
       <c r="D297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
-        <v>45324</v>
+        <v>45326</v>
       </c>
       <c r="B298" t="n">
         <v>40.55452244905271</v>
@@ -4609,12 +4609,12 @@
         <v>2.06483867810149</v>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
-        <v>45331</v>
+        <v>45333</v>
       </c>
       <c r="B299" t="n">
         <v>40.19910150049324</v>
@@ -4623,12 +4623,12 @@
         <v>1.947159392321354</v>
       </c>
       <c r="D299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="B300" t="n">
         <v>46.63085767587651</v>
@@ -4637,12 +4637,12 @@
         <v>6.284312238611389</v>
       </c>
       <c r="D300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
-        <v>45345</v>
+        <v>45347</v>
       </c>
       <c r="B301" t="n">
         <v>44.60865877693788</v>
@@ -4651,12 +4651,12 @@
         <v>5.553241268827043</v>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
-        <v>45352</v>
+        <v>45354</v>
       </c>
       <c r="B302" t="n">
         <v>44.04722915960918</v>
@@ -4665,12 +4665,12 @@
         <v>3.830264980198515</v>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
-        <v>45359</v>
+        <v>45361</v>
       </c>
       <c r="B303" t="n">
         <v>44.14142798196585</v>
@@ -4679,12 +4679,12 @@
         <v>3.934185408422909</v>
       </c>
       <c r="D303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
-        <v>45366</v>
+        <v>45368</v>
       </c>
       <c r="B304" t="n">
         <v>44.02489208198023</v>
@@ -4693,12 +4693,12 @@
         <v>3.182709600483966</v>
       </c>
       <c r="D304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
-        <v>45373</v>
+        <v>45375</v>
       </c>
       <c r="B305" t="n">
         <v>46.69045293568055</v>
@@ -4707,12 +4707,12 @@
         <v>5.081303092179391</v>
       </c>
       <c r="D305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
-        <v>45380</v>
+        <v>45382</v>
       </c>
       <c r="B306" t="n">
         <v>46.69360966547973</v>
@@ -4721,12 +4721,12 @@
         <v>5.384695604684671</v>
       </c>
       <c r="D306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
-        <v>45387</v>
+        <v>45389</v>
       </c>
       <c r="B307" t="n">
         <v>47.67982633166462</v>
@@ -4735,12 +4735,12 @@
         <v>5.79864791244048</v>
       </c>
       <c r="D307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
-        <v>45394</v>
+        <v>45396</v>
       </c>
       <c r="B308" t="n">
         <v>48.1568895063</v>
@@ -4749,12 +4749,12 @@
         <v>6.444764185412319</v>
       </c>
       <c r="D308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
-        <v>45401</v>
+        <v>45403</v>
       </c>
       <c r="B309" t="n">
         <v>47.79711932646774</v>
@@ -4763,12 +4763,12 @@
         <v>6.651849450599925</v>
       </c>
       <c r="D309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
-        <v>45408</v>
+        <v>45410</v>
       </c>
       <c r="B310" t="n">
         <v>48.38065468951697</v>
@@ -4777,12 +4777,12 @@
         <v>7.893321635132364</v>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
-        <v>45415</v>
+        <v>45417</v>
       </c>
       <c r="B311" t="n">
         <v>48.99133630322263</v>
@@ -4791,12 +4791,12 @@
         <v>8.683052881839993</v>
       </c>
       <c r="D311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
-        <v>45422</v>
+        <v>45424</v>
       </c>
       <c r="B312" t="n">
         <v>48.66486090583955</v>
@@ -4805,12 +4805,12 @@
         <v>9.129440928279902</v>
       </c>
       <c r="D312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
-        <v>45429</v>
+        <v>45431</v>
       </c>
       <c r="B313" t="n">
         <v>48.24508916114465</v>
@@ -4819,12 +4819,12 @@
         <v>8.770608752577449</v>
       </c>
       <c r="D313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
-        <v>45436</v>
+        <v>45438</v>
       </c>
       <c r="B314" t="n">
         <v>48.65356753846071</v>
@@ -4833,12 +4833,12 @@
         <v>9.146730297382479</v>
       </c>
       <c r="D314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
-        <v>45443</v>
+        <v>45445</v>
       </c>
       <c r="B315" t="n">
         <v>48.41676656337011</v>
@@ -4847,12 +4847,12 @@
         <v>8.512924380148716</v>
       </c>
       <c r="D315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
-        <v>45450</v>
+        <v>45452</v>
       </c>
       <c r="B316" t="n">
         <v>49.23584042425813</v>
@@ -4861,12 +4861,12 @@
         <v>9.33242532640749</v>
       </c>
       <c r="D316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
-        <v>45457</v>
+        <v>45459</v>
       </c>
       <c r="B317" t="n">
         <v>48.93196651223482</v>
@@ -4875,12 +4875,12 @@
         <v>8.917112512015697</v>
       </c>
       <c r="D317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
-        <v>45464</v>
+        <v>45466</v>
       </c>
       <c r="B318" t="n">
         <v>48.91572143670194</v>
@@ -4889,12 +4889,12 @@
         <v>9.014066176419256</v>
       </c>
       <c r="D318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c r="B319" t="n">
         <v>48.77036710117896</v>
@@ -4903,12 +4903,12 @@
         <v>8.036548432681659</v>
       </c>
       <c r="D319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
-        <v>45478</v>
+        <v>45480</v>
       </c>
       <c r="B320" t="n">
         <v>49.02824375412691</v>
@@ -4917,12 +4917,12 @@
         <v>8.636946029310598</v>
       </c>
       <c r="D320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
-        <v>45485</v>
+        <v>45487</v>
       </c>
       <c r="B321" t="n">
         <v>49.49776225470214</v>
@@ -4931,12 +4931,12 @@
         <v>8.880601729380997</v>
       </c>
       <c r="D321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
-        <v>45492</v>
+        <v>45494</v>
       </c>
       <c r="B322" t="n">
         <v>50.16315572519375</v>
@@ -4945,12 +4945,12 @@
         <v>9.282692103015048</v>
       </c>
       <c r="D322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
-        <v>45499</v>
+        <v>45501</v>
       </c>
       <c r="B323" t="n">
         <v>50.27993245838272</v>
@@ -4959,12 +4959,12 @@
         <v>9.559531595304477</v>
       </c>
       <c r="D323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
-        <v>45506</v>
+        <v>45508</v>
       </c>
       <c r="B324" t="n">
         <v>51.35235785507199</v>
@@ -4973,12 +4973,12 @@
         <v>9.476715215800645</v>
       </c>
       <c r="D324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
-        <v>45513</v>
+        <v>45515</v>
       </c>
       <c r="B325" t="n">
         <v>51.17688520425691</v>
@@ -4987,12 +4987,12 @@
         <v>9.187800431701076</v>
       </c>
       <c r="D325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
-        <v>45520</v>
+        <v>45522</v>
       </c>
       <c r="B326" t="n">
         <v>51.13549109636266</v>
@@ -5001,12 +5001,12 @@
         <v>8.816166816664303</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
-        <v>45527</v>
+        <v>45529</v>
       </c>
       <c r="B327" t="n">
         <v>49.81714431244333</v>
@@ -5015,12 +5015,12 @@
         <v>8.44475122035842</v>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
-        <v>45534</v>
+        <v>45536</v>
       </c>
       <c r="B328" t="n">
         <v>49.62185616196148</v>
@@ -5029,12 +5029,12 @@
         <v>8.710692602881915</v>
       </c>
       <c r="D328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
-        <v>45541</v>
+        <v>45543</v>
       </c>
       <c r="B329" t="n">
         <v>48.7892403888119</v>
@@ -5043,12 +5043,12 @@
         <v>8.414133869053549</v>
       </c>
       <c r="D329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
-        <v>45548</v>
+        <v>45550</v>
       </c>
       <c r="B330" t="n">
         <v>50.64735612468245</v>
@@ -5057,12 +5057,12 @@
         <v>10.30540803165764</v>
       </c>
       <c r="D330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
-        <v>45555</v>
+        <v>45557</v>
       </c>
       <c r="B331" t="n">
         <v>50.51799851951055</v>
@@ -5071,12 +5071,12 @@
         <v>10.08645944824261</v>
       </c>
       <c r="D331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
-        <v>45562</v>
+        <v>45564</v>
       </c>
       <c r="B332" t="n">
         <v>51.08320945950641</v>
@@ -5085,12 +5085,12 @@
         <v>10.97333596512819</v>
       </c>
       <c r="D332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
-        <v>45569</v>
+        <v>45571</v>
       </c>
       <c r="B333" t="n">
         <v>51.0941610160197</v>
@@ -5099,12 +5099,12 @@
         <v>11.03095457510493</v>
       </c>
       <c r="D333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
-        <v>45576</v>
+        <v>45578</v>
       </c>
       <c r="B334" t="n">
         <v>50.80625239789995</v>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
-        <v>45583</v>
+        <v>45585</v>
       </c>
       <c r="B335" t="n">
         <v>51.05214004925254</v>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
-        <v>45590</v>
+        <v>45592</v>
       </c>
       <c r="B336" t="n">
         <v>51.32575447627008</v>
@@ -5146,7 +5146,7 @@
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
-        <v>45597</v>
+        <v>45599</v>
       </c>
       <c r="B337" t="n">
         <v>51.28981261576786</v>
@@ -5160,7 +5160,7 @@
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
-        <v>45604</v>
+        <v>45606</v>
       </c>
       <c r="B338" t="n">
         <v>51.88724867478436</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
-        <v>45611</v>
+        <v>45613</v>
       </c>
       <c r="B339" t="n">
         <v>52.61981037643444</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
-        <v>45618</v>
+        <v>45620</v>
       </c>
       <c r="B340" t="n">
         <v>52.26166986965671</v>
@@ -5202,7 +5202,7 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="B341" t="n">
         <v>52.29199869918524</v>
@@ -5216,7 +5216,7 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="B342" t="n">
         <v>52.32761887937897</v>
@@ -5230,7 +5230,7 @@
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
-        <v>45639</v>
+        <v>45641</v>
       </c>
       <c r="B343" t="n">
         <v>51.88399491041667</v>
@@ -5244,7 +5244,7 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
-        <v>45646</v>
+        <v>45648</v>
       </c>
       <c r="B344" t="n">
         <v>52.20378416280028</v>
@@ -5258,7 +5258,7 @@
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
-        <v>45653</v>
+        <v>45655</v>
       </c>
       <c r="B345" t="n">
         <v>53.11503365282314</v>
@@ -5272,7 +5272,7 @@
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="B346" t="n">
         <v>53.37059918633443</v>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
-        <v>45667</v>
+        <v>45669</v>
       </c>
       <c r="B347" t="n">
         <v>53.85373825463236</v>
@@ -5300,7 +5300,7 @@
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
-        <v>45674</v>
+        <v>45676</v>
       </c>
       <c r="B348" t="n">
         <v>54.16999727647271</v>
@@ -5314,7 +5314,7 @@
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
-        <v>45681</v>
+        <v>45683</v>
       </c>
       <c r="B349" t="n">
         <v>54.55807648837421</v>
@@ -5328,7 +5328,7 @@
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>45688</v>
+        <v>45690</v>
       </c>
       <c r="B350" t="n">
         <v>55.0255238019496</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>45695</v>
+        <v>45697</v>
       </c>
       <c r="B351" t="n">
         <v>52.15276543132126</v>
@@ -5356,7 +5356,7 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>45702</v>
+        <v>45704</v>
       </c>
       <c r="B352" t="n">
         <v>53.46539259330563</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>45709</v>
+        <v>45711</v>
       </c>
       <c r="B353" t="n">
         <v>52.89396470901855</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>45716</v>
+        <v>45718</v>
       </c>
       <c r="B354" t="n">
         <v>53.33313178583774</v>
@@ -5398,7 +5398,7 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>45723</v>
+        <v>45725</v>
       </c>
       <c r="B355" t="n">
         <v>53.83058166380598</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>45730</v>
+        <v>45732</v>
       </c>
       <c r="B356" t="n">
         <v>51.25373013295917</v>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>45737</v>
+        <v>45739</v>
       </c>
       <c r="B357" t="n">
         <v>51.33203572632763</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>45744</v>
+        <v>45746</v>
       </c>
       <c r="B358" t="n">
         <v>51.02811046532725</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>45751</v>
+        <v>45753</v>
       </c>
       <c r="B359" t="n">
         <v>50.54922492965142</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>45758</v>
+        <v>45760</v>
       </c>
       <c r="B360" t="n">
         <v>50.75795418177012</v>
@@ -5482,7 +5482,7 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>45765</v>
+        <v>45767</v>
       </c>
       <c r="B361" t="n">
         <v>50.88634932688904</v>
@@ -5496,7 +5496,7 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>45772</v>
+        <v>45774</v>
       </c>
       <c r="B362" t="n">
         <v>52.50728263240956</v>
@@ -5510,7 +5510,7 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>45779</v>
+        <v>45781</v>
       </c>
       <c r="B363" t="n">
         <v>51.13624715591921</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>45786</v>
+        <v>45788</v>
       </c>
       <c r="B364" t="n">
         <v>51.74718932312701</v>
@@ -5538,7 +5538,7 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>45793</v>
+        <v>45795</v>
       </c>
       <c r="B365" t="n">
         <v>51.64581757653783</v>
@@ -5552,7 +5552,7 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>45800</v>
+        <v>45802</v>
       </c>
       <c r="B366" t="n">
         <v>51.95817568328309</v>
@@ -5566,7 +5566,7 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>45807</v>
+        <v>45809</v>
       </c>
       <c r="B367" t="n">
         <v>52.45300210206849</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>45814</v>
+        <v>45816</v>
       </c>
       <c r="B368" t="n">
         <v>53.53504595468252</v>
@@ -5594,7 +5594,7 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>45821</v>
+        <v>45823</v>
       </c>
       <c r="B369" t="n">
         <v>53.52311974463336</v>
@@ -5608,7 +5608,7 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>45828</v>
+        <v>45830</v>
       </c>
       <c r="B370" t="n">
         <v>53.15837879676144</v>
@@ -5622,7 +5622,7 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>45835</v>
+        <v>45837</v>
       </c>
       <c r="B371" t="n">
         <v>53.62689226655666</v>
@@ -5636,7 +5636,7 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>45842</v>
+        <v>45844</v>
       </c>
       <c r="B372" t="n">
         <v>53.71390964646638</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>45849</v>
+        <v>45851</v>
       </c>
       <c r="B373" t="n">
         <v>53.53406517280592</v>

--- a/output/tables/rolling_dy_results.xlsx
+++ b/output/tables/rolling_dy_results.xlsx
@@ -459,10 +459,10 @@
         <v>43252</v>
       </c>
       <c r="B2" t="n">
-        <v>40.3047253325484</v>
+        <v>44.84281012095899</v>
       </c>
       <c r="C2" t="n">
-        <v>2.794981156144892</v>
+        <v>3.985935963447814</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -473,10 +473,10 @@
         <v>43259</v>
       </c>
       <c r="B3" t="n">
-        <v>42.32252154244109</v>
+        <v>46.40096597679966</v>
       </c>
       <c r="C3" t="n">
-        <v>3.230914347445534</v>
+        <v>4.744304516000593</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -487,10 +487,10 @@
         <v>43266</v>
       </c>
       <c r="B4" t="n">
-        <v>42.0000934050918</v>
+        <v>46.38815651366061</v>
       </c>
       <c r="C4" t="n">
-        <v>3.170584799920313</v>
+        <v>4.678730098407023</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -501,10 +501,10 @@
         <v>43273</v>
       </c>
       <c r="B5" t="n">
-        <v>45.56721520460555</v>
+        <v>48.1126327028915</v>
       </c>
       <c r="C5" t="n">
-        <v>4.400406725363971</v>
+        <v>5.126858691628959</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -515,10 +515,10 @@
         <v>43280</v>
       </c>
       <c r="B6" t="n">
-        <v>45.70636336557816</v>
+        <v>49.12369113972832</v>
       </c>
       <c r="C6" t="n">
-        <v>3.321464133687602</v>
+        <v>2.902389499360726</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -529,10 +529,10 @@
         <v>43287</v>
       </c>
       <c r="B7" t="n">
-        <v>45.09228353533691</v>
+        <v>48.67664617232688</v>
       </c>
       <c r="C7" t="n">
-        <v>3.639727602473175</v>
+        <v>2.639531051108001</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -543,10 +543,10 @@
         <v>43294</v>
       </c>
       <c r="B8" t="n">
-        <v>44.9279947663513</v>
+        <v>48.5020246347529</v>
       </c>
       <c r="C8" t="n">
-        <v>4.557519172981807</v>
+        <v>2.808326928072022</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -557,10 +557,10 @@
         <v>43301</v>
       </c>
       <c r="B9" t="n">
-        <v>45.12686319979852</v>
+        <v>49.18406995034857</v>
       </c>
       <c r="C9" t="n">
-        <v>4.620092400728858</v>
+        <v>2.826926163612692</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -571,10 +571,10 @@
         <v>43308</v>
       </c>
       <c r="B10" t="n">
-        <v>45.52238395367745</v>
+        <v>49.58341845004526</v>
       </c>
       <c r="C10" t="n">
-        <v>5.185648659240496</v>
+        <v>4.664102157415734</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>43315</v>
       </c>
       <c r="B11" t="n">
-        <v>46.08262345328529</v>
+        <v>49.83960589907102</v>
       </c>
       <c r="C11" t="n">
-        <v>5.526708447784451</v>
+        <v>4.517643264883493</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -599,10 +599,10 @@
         <v>43322</v>
       </c>
       <c r="B12" t="n">
-        <v>45.78962142952789</v>
+        <v>48.46863854613759</v>
       </c>
       <c r="C12" t="n">
-        <v>4.273873844556628</v>
+        <v>2.952582782185353</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -613,10 +613,10 @@
         <v>43329</v>
       </c>
       <c r="B13" t="n">
-        <v>45.1392103183995</v>
+        <v>47.87519090036982</v>
       </c>
       <c r="C13" t="n">
-        <v>4.053269326582204</v>
+        <v>2.920697734518183</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -627,10 +627,10 @@
         <v>43336</v>
       </c>
       <c r="B14" t="n">
-        <v>44.78265753201893</v>
+        <v>47.51127044361036</v>
       </c>
       <c r="C14" t="n">
-        <v>3.843144028657147</v>
+        <v>2.826572469961363</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>43343</v>
       </c>
       <c r="B15" t="n">
-        <v>44.81819876294222</v>
+        <v>47.53557467223476</v>
       </c>
       <c r="C15" t="n">
-        <v>4.128833391431666</v>
+        <v>3.025917084046836</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -655,10 +655,10 @@
         <v>43350</v>
       </c>
       <c r="B16" t="n">
-        <v>44.51415181055922</v>
+        <v>47.64763224510947</v>
       </c>
       <c r="C16" t="n">
-        <v>4.298729133858766</v>
+        <v>3.378023461053544</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -669,10 +669,10 @@
         <v>43357</v>
       </c>
       <c r="B17" t="n">
-        <v>44.53059408302656</v>
+        <v>47.66160314349492</v>
       </c>
       <c r="C17" t="n">
-        <v>3.975307755412161</v>
+        <v>3.419879490914303</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -683,10 +683,10 @@
         <v>43364</v>
       </c>
       <c r="B18" t="n">
-        <v>45.8378306598567</v>
+        <v>49.04761241688166</v>
       </c>
       <c r="C18" t="n">
-        <v>4.053644347166124</v>
+        <v>3.437762761599978</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>43371</v>
       </c>
       <c r="B19" t="n">
-        <v>46.21160699501065</v>
+        <v>49.00292651904828</v>
       </c>
       <c r="C19" t="n">
-        <v>4.453301385298256</v>
+        <v>3.185562897967285</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -711,10 +711,10 @@
         <v>43378</v>
       </c>
       <c r="B20" t="n">
-        <v>46.74602300380661</v>
+        <v>49.14520396141823</v>
       </c>
       <c r="C20" t="n">
-        <v>5.12174178346788</v>
+        <v>3.038188844394846</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -725,10 +725,10 @@
         <v>43385</v>
       </c>
       <c r="B21" t="n">
-        <v>46.93881473016115</v>
+        <v>49.73190007585547</v>
       </c>
       <c r="C21" t="n">
-        <v>4.889866319283809</v>
+        <v>3.042015782266386</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -739,10 +739,10 @@
         <v>43392</v>
       </c>
       <c r="B22" t="n">
-        <v>47.82848264036895</v>
+        <v>49.97206066236089</v>
       </c>
       <c r="C22" t="n">
-        <v>5.73152017452533</v>
+        <v>3.091881842921734</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>43399</v>
       </c>
       <c r="B23" t="n">
-        <v>49.0673046285038</v>
+        <v>50.99000886504505</v>
       </c>
       <c r="C23" t="n">
-        <v>6.201139136517186</v>
+        <v>2.971896740288513</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -767,10 +767,10 @@
         <v>43406</v>
       </c>
       <c r="B24" t="n">
-        <v>48.91859094044305</v>
+        <v>51.18574043991165</v>
       </c>
       <c r="C24" t="n">
-        <v>5.903858253360506</v>
+        <v>2.759748725758065</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -781,10 +781,10 @@
         <v>43413</v>
       </c>
       <c r="B25" t="n">
-        <v>48.68157913556809</v>
+        <v>50.52040712663928</v>
       </c>
       <c r="C25" t="n">
-        <v>5.829809820654999</v>
+        <v>2.708508689111112</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
@@ -795,10 +795,10 @@
         <v>43420</v>
       </c>
       <c r="B26" t="n">
-        <v>49.8111198565704</v>
+        <v>50.82569629694592</v>
       </c>
       <c r="C26" t="n">
-        <v>5.638063932618167</v>
+        <v>2.334944616799611</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>43427</v>
       </c>
       <c r="B27" t="n">
-        <v>51.37150547584673</v>
+        <v>52.47724501904118</v>
       </c>
       <c r="C27" t="n">
-        <v>4.931576345553304</v>
+        <v>1.852686429990163</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -823,10 +823,10 @@
         <v>43434</v>
       </c>
       <c r="B28" t="n">
-        <v>52.44213523704217</v>
+        <v>52.76944537225375</v>
       </c>
       <c r="C28" t="n">
-        <v>6.03772543435434</v>
+        <v>2.280078172152331</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>43441</v>
       </c>
       <c r="B29" t="n">
-        <v>49.90568223455489</v>
+        <v>52.69634519453064</v>
       </c>
       <c r="C29" t="n">
-        <v>2.760299400027247</v>
+        <v>1.893261926730913</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -851,10 +851,10 @@
         <v>43448</v>
       </c>
       <c r="B30" t="n">
-        <v>50.4376249297511</v>
+        <v>53.19508551603496</v>
       </c>
       <c r="C30" t="n">
-        <v>2.884512080053038</v>
+        <v>1.905210499108692</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
         <v>43455</v>
       </c>
       <c r="B31" t="n">
-        <v>49.55543626010058</v>
+        <v>52.22998800919738</v>
       </c>
       <c r="C31" t="n">
-        <v>3.277473427439221</v>
+        <v>1.98577593490461</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -879,10 +879,10 @@
         <v>43462</v>
       </c>
       <c r="B32" t="n">
-        <v>49.54800299862551</v>
+        <v>52.17293802591325</v>
       </c>
       <c r="C32" t="n">
-        <v>3.432029101236636</v>
+        <v>2.105650027405278</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>43469</v>
       </c>
       <c r="B33" t="n">
-        <v>50.55987263486142</v>
+        <v>52.59824209054504</v>
       </c>
       <c r="C33" t="n">
-        <v>3.757052291408412</v>
+        <v>2.021883045158861</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -907,10 +907,10 @@
         <v>43476</v>
       </c>
       <c r="B34" t="n">
-        <v>50.08875004779549</v>
+        <v>52.04802761512448</v>
       </c>
       <c r="C34" t="n">
-        <v>3.734451975732788</v>
+        <v>2.011045942851414</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>43483</v>
       </c>
       <c r="B35" t="n">
-        <v>49.75831509221572</v>
+        <v>51.65347122754286</v>
       </c>
       <c r="C35" t="n">
-        <v>3.591212452269512</v>
+        <v>1.790161762212643</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -935,10 +935,10 @@
         <v>43490</v>
       </c>
       <c r="B36" t="n">
-        <v>49.27247499116832</v>
+        <v>51.24048242020308</v>
       </c>
       <c r="C36" t="n">
-        <v>3.57235768157594</v>
+        <v>1.661064838884933</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>43497</v>
       </c>
       <c r="B37" t="n">
-        <v>49.7708125131546</v>
+        <v>51.55867671501311</v>
       </c>
       <c r="C37" t="n">
-        <v>3.922133638527051</v>
+        <v>1.96943821574568</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>43504</v>
       </c>
       <c r="B38" t="n">
-        <v>49.87667736822939</v>
+        <v>51.16748621812823</v>
       </c>
       <c r="C38" t="n">
-        <v>4.231132740161013</v>
+        <v>2.222263205060878</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         <v>43511</v>
       </c>
       <c r="B39" t="n">
-        <v>50.08416574247244</v>
+        <v>51.69135435974468</v>
       </c>
       <c r="C39" t="n">
-        <v>3.620285127821986</v>
+        <v>2.319211344762343</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -991,10 +991,10 @@
         <v>43518</v>
       </c>
       <c r="B40" t="n">
-        <v>49.61755241533907</v>
+        <v>51.27190743427835</v>
       </c>
       <c r="C40" t="n">
-        <v>3.838213719135561</v>
+        <v>2.41747272856181</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1005,10 +1005,10 @@
         <v>43525</v>
       </c>
       <c r="B41" t="n">
-        <v>49.27905360052324</v>
+        <v>51.4126385057227</v>
       </c>
       <c r="C41" t="n">
-        <v>4.163481226956225</v>
+        <v>2.506297520069964</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
         <v>43532</v>
       </c>
       <c r="B42" t="n">
-        <v>48.90781759637128</v>
+        <v>51.39292902865269</v>
       </c>
       <c r="C42" t="n">
-        <v>4.451548552820068</v>
+        <v>2.616122077689007</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>43539</v>
       </c>
       <c r="B43" t="n">
-        <v>47.99480654666373</v>
+        <v>50.81706060272308</v>
       </c>
       <c r="C43" t="n">
-        <v>3.777222513941942</v>
+        <v>2.028584665486578</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1047,10 +1047,10 @@
         <v>43546</v>
       </c>
       <c r="B44" t="n">
-        <v>47.92924051588929</v>
+        <v>50.95424760068612</v>
       </c>
       <c r="C44" t="n">
-        <v>3.799489959862894</v>
+        <v>2.184801255653577</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>43553</v>
       </c>
       <c r="B45" t="n">
-        <v>45.63802939024621</v>
+        <v>49.42004079395358</v>
       </c>
       <c r="C45" t="n">
-        <v>3.447841583853155</v>
+        <v>2.603928133112707</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1075,10 +1075,10 @@
         <v>43560</v>
       </c>
       <c r="B46" t="n">
-        <v>44.72348416673808</v>
+        <v>48.96304832532022</v>
       </c>
       <c r="C46" t="n">
-        <v>3.364022298994763</v>
+        <v>2.585007683180391</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>43567</v>
       </c>
       <c r="B47" t="n">
-        <v>43.5276516644731</v>
+        <v>47.90377210670931</v>
       </c>
       <c r="C47" t="n">
-        <v>3.994798151454786</v>
+        <v>3.75668986737964</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>43574</v>
       </c>
       <c r="B48" t="n">
-        <v>44.16059086289004</v>
+        <v>48.31590200257605</v>
       </c>
       <c r="C48" t="n">
-        <v>2.734512985230562</v>
+        <v>2.797763629554357</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1117,10 +1117,10 @@
         <v>43581</v>
       </c>
       <c r="B49" t="n">
-        <v>44.42756861321941</v>
+        <v>48.53558251279409</v>
       </c>
       <c r="C49" t="n">
-        <v>2.863319655257053</v>
+        <v>2.885656470968531</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1131,10 +1131,10 @@
         <v>43588</v>
       </c>
       <c r="B50" t="n">
-        <v>45.37510052417425</v>
+        <v>49.01166472427261</v>
       </c>
       <c r="C50" t="n">
-        <v>3.591453007218706</v>
+        <v>2.87037351426781</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1145,10 +1145,10 @@
         <v>43595</v>
       </c>
       <c r="B51" t="n">
-        <v>45.82732142109804</v>
+        <v>49.19539345681779</v>
       </c>
       <c r="C51" t="n">
-        <v>3.082616904483323</v>
+        <v>2.649325563694893</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>43602</v>
       </c>
       <c r="B52" t="n">
-        <v>45.95980643291308</v>
+        <v>49.27784998116315</v>
       </c>
       <c r="C52" t="n">
-        <v>3.045099529782842</v>
+        <v>2.573399890180764</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
         <v>43609</v>
       </c>
       <c r="B53" t="n">
-        <v>45.77582436790806</v>
+        <v>48.82735555114454</v>
       </c>
       <c r="C53" t="n">
-        <v>3.0611480663836</v>
+        <v>2.807831971752131</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1187,10 +1187,10 @@
         <v>43616</v>
       </c>
       <c r="B54" t="n">
-        <v>42.77130080772565</v>
+        <v>46.36337531012723</v>
       </c>
       <c r="C54" t="n">
-        <v>1.649904270105619</v>
+        <v>1.510848775000406</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>43623</v>
       </c>
       <c r="B55" t="n">
-        <v>43.97035412937972</v>
+        <v>47.56253758254039</v>
       </c>
       <c r="C55" t="n">
-        <v>1.958059553880217</v>
+        <v>2.131907124826462</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>43630</v>
       </c>
       <c r="B56" t="n">
-        <v>43.87688852565742</v>
+        <v>46.74643455771869</v>
       </c>
       <c r="C56" t="n">
-        <v>1.812261434267985</v>
+        <v>2.332036406629972</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -1229,10 +1229,10 @@
         <v>43637</v>
       </c>
       <c r="B57" t="n">
-        <v>44.1590156597878</v>
+        <v>46.9483238888474</v>
       </c>
       <c r="C57" t="n">
-        <v>1.699932914261235</v>
+        <v>2.203287523677817</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1243,10 +1243,10 @@
         <v>43644</v>
       </c>
       <c r="B58" t="n">
-        <v>44.80904474178603</v>
+        <v>47.94801626364039</v>
       </c>
       <c r="C58" t="n">
-        <v>1.31612904080443</v>
+        <v>2.467769027317955</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1257,10 +1257,10 @@
         <v>43651</v>
       </c>
       <c r="B59" t="n">
-        <v>45.6305109684792</v>
+        <v>47.64558707215284</v>
       </c>
       <c r="C59" t="n">
-        <v>1.257425325087563</v>
+        <v>2.438854130075335</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1271,10 +1271,10 @@
         <v>43658</v>
       </c>
       <c r="B60" t="n">
-        <v>45.53372504347245</v>
+        <v>56.8950209623944</v>
       </c>
       <c r="C60" t="n">
-        <v>1.214319125139525</v>
+        <v>6.294034071962148</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1285,10 +1285,10 @@
         <v>43665</v>
       </c>
       <c r="B61" t="n">
-        <v>45.56635393264309</v>
+        <v>48.08673796115934</v>
       </c>
       <c r="C61" t="n">
-        <v>1.134103291326497</v>
+        <v>1.869034869098531</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>43672</v>
       </c>
       <c r="B62" t="n">
-        <v>45.43868041558085</v>
+        <v>48.37235956477324</v>
       </c>
       <c r="C62" t="n">
-        <v>1.212520110418734</v>
+        <v>1.770214160102897</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1313,10 +1313,10 @@
         <v>43679</v>
       </c>
       <c r="B63" t="n">
-        <v>64.65363545189813</v>
+        <v>59.48584428647592</v>
       </c>
       <c r="C63" t="n">
-        <v>12.07661825145439</v>
+        <v>10.89763611646946</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
         <v>43686</v>
       </c>
       <c r="B64" t="n">
-        <v>45.55507123333996</v>
+        <v>59.41021712671638</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9525386746538204</v>
+        <v>11.18500514499455</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -1341,10 +1341,10 @@
         <v>43693</v>
       </c>
       <c r="B65" t="n">
-        <v>65.47246997952728</v>
+        <v>49.23009997820797</v>
       </c>
       <c r="C65" t="n">
-        <v>11.87443899299261</v>
+        <v>1.554755805190824</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>43700</v>
       </c>
       <c r="B66" t="n">
-        <v>64.18874971031899</v>
+        <v>60.64570071847832</v>
       </c>
       <c r="C66" t="n">
-        <v>11.59576252707683</v>
+        <v>11.95884903288852</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>43707</v>
       </c>
       <c r="B67" t="n">
-        <v>63.96746082997115</v>
+        <v>49.45117382337413</v>
       </c>
       <c r="C67" t="n">
-        <v>10.97218257404675</v>
+        <v>1.894882991000064</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         <v>43714</v>
       </c>
       <c r="B68" t="n">
-        <v>64.2265514080412</v>
+        <v>49.96006557407401</v>
       </c>
       <c r="C68" t="n">
-        <v>12.24122554333093</v>
+        <v>2.000547132652352</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>43721</v>
       </c>
       <c r="B69" t="n">
-        <v>68.70350527194243</v>
+        <v>53.2520347565129</v>
       </c>
       <c r="C69" t="n">
-        <v>15.95515873699208</v>
+        <v>2.544393931393035</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -1411,10 +1411,10 @@
         <v>43728</v>
       </c>
       <c r="B70" t="n">
-        <v>67.50095137888115</v>
+        <v>64.14654950100173</v>
       </c>
       <c r="C70" t="n">
-        <v>13.13372383779121</v>
+        <v>15.96778705085276</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -1425,10 +1425,10 @@
         <v>43735</v>
       </c>
       <c r="B71" t="n">
-        <v>76.26326161553088</v>
+        <v>77.844702931258</v>
       </c>
       <c r="C71" t="n">
-        <v>11.25892348568481</v>
+        <v>11.68949593630224</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -1439,10 +1439,10 @@
         <v>43742</v>
       </c>
       <c r="B72" t="n">
-        <v>73.02480864186919</v>
+        <v>69.67671310734686</v>
       </c>
       <c r="C72" t="n">
-        <v>13.4010355889355</v>
+        <v>13.05522253919306</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>43749</v>
       </c>
       <c r="B73" t="n">
-        <v>72.90397352873528</v>
+        <v>69.21549350173241</v>
       </c>
       <c r="C73" t="n">
-        <v>12.68316695962927</v>
+        <v>12.52865289565788</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -1467,10 +1467,10 @@
         <v>43756</v>
       </c>
       <c r="B74" t="n">
-        <v>72.33296796264412</v>
+        <v>69.22464834513745</v>
       </c>
       <c r="C74" t="n">
-        <v>13.85240026141378</v>
+        <v>12.25580765763459</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
         <v>43763</v>
       </c>
       <c r="B75" t="n">
-        <v>70.62290614321482</v>
+        <v>69.47497520686296</v>
       </c>
       <c r="C75" t="n">
-        <v>11.83635420005701</v>
+        <v>12.16824473123514</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -1495,10 +1495,10 @@
         <v>43770</v>
       </c>
       <c r="B76" t="n">
-        <v>71.8668289707966</v>
+        <v>68.92225377575787</v>
       </c>
       <c r="C76" t="n">
-        <v>12.15326789528847</v>
+        <v>11.72973688811207</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1509,10 +1509,10 @@
         <v>43777</v>
       </c>
       <c r="B77" t="n">
-        <v>71.90573239367214</v>
+        <v>68.22859152571591</v>
       </c>
       <c r="C77" t="n">
-        <v>14.12945021265801</v>
+        <v>11.9164700391965</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         <v>43784</v>
       </c>
       <c r="B78" t="n">
-        <v>73.41518613687198</v>
+        <v>68.96963643866025</v>
       </c>
       <c r="C78" t="n">
-        <v>15.47680592539419</v>
+        <v>13.10866243606376</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>43791</v>
       </c>
       <c r="B79" t="n">
-        <v>71.67356360174885</v>
+        <v>68.82355927511198</v>
       </c>
       <c r="C79" t="n">
-        <v>14.72020583907144</v>
+        <v>12.8167920300815</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>43798</v>
       </c>
       <c r="B80" t="n">
-        <v>71.93205393213343</v>
+        <v>68.97633888638143</v>
       </c>
       <c r="C80" t="n">
-        <v>14.17551185309097</v>
+        <v>13.36500532747556</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>43805</v>
       </c>
       <c r="B81" t="n">
-        <v>72.32188830253692</v>
+        <v>69.10835517394561</v>
       </c>
       <c r="C81" t="n">
-        <v>13.83950247415883</v>
+        <v>13.47794648693074</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>43812</v>
       </c>
       <c r="B82" t="n">
-        <v>72.06151122706765</v>
+        <v>69.62523234568</v>
       </c>
       <c r="C82" t="n">
-        <v>13.65435087860101</v>
+        <v>14.39634564351984</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -1593,10 +1593,10 @@
         <v>43819</v>
       </c>
       <c r="B83" t="n">
-        <v>73.79603553338202</v>
+        <v>69.36135756993089</v>
       </c>
       <c r="C83" t="n">
-        <v>12.36629492970436</v>
+        <v>13.46350375751955</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -1607,10 +1607,10 @@
         <v>43826</v>
       </c>
       <c r="B84" t="n">
-        <v>70.94041934615609</v>
+        <v>68.51512898831912</v>
       </c>
       <c r="C84" t="n">
-        <v>14.16308933904078</v>
+        <v>11.8018971643805</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -1621,10 +1621,10 @@
         <v>43833</v>
       </c>
       <c r="B85" t="n">
-        <v>71.76129645336272</v>
+        <v>69.19121611925931</v>
       </c>
       <c r="C85" t="n">
-        <v>14.42536633976851</v>
+        <v>13.89909515388289</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>43840</v>
       </c>
       <c r="B86" t="n">
-        <v>70.98291442617435</v>
+        <v>68.44319765882004</v>
       </c>
       <c r="C86" t="n">
-        <v>14.91181645303148</v>
+        <v>12.89021443146232</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>43847</v>
       </c>
       <c r="B87" t="n">
-        <v>68.73525337997847</v>
+        <v>68.15979857795315</v>
       </c>
       <c r="C87" t="n">
-        <v>11.65052946597259</v>
+        <v>11.92689015878721</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -1663,10 +1663,10 @@
         <v>43854</v>
       </c>
       <c r="B88" t="n">
-        <v>68.56032885905118</v>
+        <v>68.48885106587147</v>
       </c>
       <c r="C88" t="n">
-        <v>12.60111548406344</v>
+        <v>12.25154329229571</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -1677,10 +1677,10 @@
         <v>43861</v>
       </c>
       <c r="B89" t="n">
-        <v>68.46966331048004</v>
+        <v>70.35121681664161</v>
       </c>
       <c r="C89" t="n">
-        <v>12.46970788049633</v>
+        <v>12.81451996387697</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -1691,10 +1691,10 @@
         <v>43868</v>
       </c>
       <c r="B90" t="n">
-        <v>68.99446656099822</v>
+        <v>68.37037686973962</v>
       </c>
       <c r="C90" t="n">
-        <v>12.29708783604078</v>
+        <v>12.54096274542986</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -1705,10 +1705,10 @@
         <v>43875</v>
       </c>
       <c r="B91" t="n">
-        <v>68.92711938775338</v>
+        <v>73.29364577668298</v>
       </c>
       <c r="C91" t="n">
-        <v>12.48240706201983</v>
+        <v>16.625576862654</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -1719,10 +1719,10 @@
         <v>43882</v>
       </c>
       <c r="B92" t="n">
-        <v>68.94660626083865</v>
+        <v>73.61818770835558</v>
       </c>
       <c r="C92" t="n">
-        <v>14.02541955139685</v>
+        <v>16.82812206497264</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>43889</v>
       </c>
       <c r="B93" t="n">
-        <v>68.17655977737228</v>
+        <v>69.83039848315057</v>
       </c>
       <c r="C93" t="n">
-        <v>12.37495056747488</v>
+        <v>11.87849065578454</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>43896</v>
       </c>
       <c r="B94" t="n">
-        <v>69.26098644934042</v>
+        <v>68.10956419962018</v>
       </c>
       <c r="C94" t="n">
-        <v>14.62164026850091</v>
+        <v>11.7985910586707</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>43903</v>
       </c>
       <c r="B95" t="n">
-        <v>68.72359909135075</v>
+        <v>68.63971556833525</v>
       </c>
       <c r="C95" t="n">
-        <v>12.8831681610775</v>
+        <v>12.07329878793512</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>43910</v>
       </c>
       <c r="B96" t="n">
-        <v>69.12803927721474</v>
+        <v>69.32530123958453</v>
       </c>
       <c r="C96" t="n">
-        <v>11.39748094865607</v>
+        <v>11.47933980013646</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
         <v>43917</v>
       </c>
       <c r="B97" t="n">
-        <v>69.45642492758456</v>
+        <v>70.99596153054914</v>
       </c>
       <c r="C97" t="n">
-        <v>11.80687613807759</v>
+        <v>12.71985938426172</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -1803,10 +1803,10 @@
         <v>43924</v>
       </c>
       <c r="B98" t="n">
-        <v>69.80444333685503</v>
+        <v>71.28161733471778</v>
       </c>
       <c r="C98" t="n">
-        <v>12.84919502412358</v>
+        <v>13.51857402747993</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -1817,10 +1817,10 @@
         <v>43931</v>
       </c>
       <c r="B99" t="n">
-        <v>70.14344236565135</v>
+        <v>71.65917026926184</v>
       </c>
       <c r="C99" t="n">
-        <v>13.1110671139739</v>
+        <v>14.3765346067076</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>43938</v>
       </c>
       <c r="B100" t="n">
-        <v>70.27398821437832</v>
+        <v>71.60212605584127</v>
       </c>
       <c r="C100" t="n">
-        <v>13.65961353085802</v>
+        <v>14.24568537293764</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -1845,10 +1845,10 @@
         <v>43945</v>
       </c>
       <c r="B101" t="n">
-        <v>70.03830053139292</v>
+        <v>68.11979127268175</v>
       </c>
       <c r="C101" t="n">
-        <v>13.57516453967142</v>
+        <v>11.22922864528879</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>43952</v>
       </c>
       <c r="B102" t="n">
-        <v>69.74115496417373</v>
+        <v>68.04203547684594</v>
       </c>
       <c r="C102" t="n">
-        <v>12.40113011757822</v>
+        <v>11.23783252434041</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -1873,10 +1873,10 @@
         <v>43959</v>
       </c>
       <c r="B103" t="n">
-        <v>69.61907296345062</v>
+        <v>70.74022628645001</v>
       </c>
       <c r="C103" t="n">
-        <v>12.77344273803895</v>
+        <v>11.52483911266255</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>43966</v>
       </c>
       <c r="B104" t="n">
-        <v>71.03949308310594</v>
+        <v>72.12910031415981</v>
       </c>
       <c r="C104" t="n">
-        <v>9.963120567113982</v>
+        <v>9.964206703974471</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -1901,10 +1901,10 @@
         <v>43973</v>
       </c>
       <c r="B105" t="n">
-        <v>70.18857362803308</v>
+        <v>70.70969147690751</v>
       </c>
       <c r="C105" t="n">
-        <v>10.4925607705414</v>
+        <v>10.01919790308822</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -1915,10 +1915,10 @@
         <v>43980</v>
       </c>
       <c r="B106" t="n">
-        <v>70.04063675872419</v>
+        <v>67.26330342002628</v>
       </c>
       <c r="C106" t="n">
-        <v>14.68992123274916</v>
+        <v>9.003613023958543</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>43987</v>
       </c>
       <c r="B107" t="n">
-        <v>70.1910215952341</v>
+        <v>71.15175406201638</v>
       </c>
       <c r="C107" t="n">
-        <v>15.04267992504461</v>
+        <v>13.13366035466645</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
         <v>43994</v>
       </c>
       <c r="B108" t="n">
-        <v>69.8357303446666</v>
+        <v>71.62374569926192</v>
       </c>
       <c r="C108" t="n">
-        <v>15.2351019166698</v>
+        <v>16.05430831098971</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -1957,10 +1957,10 @@
         <v>44001</v>
       </c>
       <c r="B109" t="n">
-        <v>68.91304800385552</v>
+        <v>74.78569319668993</v>
       </c>
       <c r="C109" t="n">
-        <v>14.64353132452278</v>
+        <v>19.67541717168815</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -1971,10 +1971,10 @@
         <v>44008</v>
       </c>
       <c r="B110" t="n">
-        <v>67.9684152486588</v>
+        <v>69.12401046106264</v>
       </c>
       <c r="C110" t="n">
-        <v>13.54011763442714</v>
+        <v>12.88045734240036</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -1985,10 +1985,10 @@
         <v>44015</v>
       </c>
       <c r="B111" t="n">
-        <v>67.82876267980457</v>
+        <v>68.90883190945026</v>
       </c>
       <c r="C111" t="n">
-        <v>13.74826465060823</v>
+        <v>12.3852283853719</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -1999,10 +1999,10 @@
         <v>44022</v>
       </c>
       <c r="B112" t="n">
-        <v>67.76093887031882</v>
+        <v>68.65092429206099</v>
       </c>
       <c r="C112" t="n">
-        <v>12.64729740540535</v>
+        <v>11.64361369268197</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>44029</v>
       </c>
       <c r="B113" t="n">
-        <v>67.46551120481682</v>
+        <v>68.11268569760661</v>
       </c>
       <c r="C113" t="n">
-        <v>13.12535781636327</v>
+        <v>10.54161613080259</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         <v>44036</v>
       </c>
       <c r="B114" t="n">
-        <v>72.17858436554548</v>
+        <v>68.51904291195062</v>
       </c>
       <c r="C114" t="n">
-        <v>30.14512118738706</v>
+        <v>11.83161914266214</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>44043</v>
       </c>
       <c r="B115" t="n">
-        <v>70.90010047026297</v>
+        <v>71.8763112054361</v>
       </c>
       <c r="C115" t="n">
-        <v>23.18396997359483</v>
+        <v>18.36288554562268</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -2055,10 +2055,10 @@
         <v>44050</v>
       </c>
       <c r="B116" t="n">
-        <v>69.89000884328847</v>
+        <v>69.78581181183672</v>
       </c>
       <c r="C116" t="n">
-        <v>16.21673456547946</v>
+        <v>13.69495874108659</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
@@ -2069,10 +2069,10 @@
         <v>44057</v>
       </c>
       <c r="B117" t="n">
-        <v>59.41266328887144</v>
+        <v>66.90015905005519</v>
       </c>
       <c r="C117" t="n">
-        <v>8.41081666646155</v>
+        <v>10.70889432087307</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
@@ -2083,10 +2083,10 @@
         <v>44064</v>
       </c>
       <c r="B118" t="n">
-        <v>58.53570781481506</v>
+        <v>66.21147951481105</v>
       </c>
       <c r="C118" t="n">
-        <v>8.578060747976265</v>
+        <v>10.28906830128112</v>
       </c>
       <c r="D118" t="n">
         <v>1</v>
@@ -2097,10 +2097,10 @@
         <v>44071</v>
       </c>
       <c r="B119" t="n">
-        <v>58.75789266383267</v>
+        <v>60.66899750200955</v>
       </c>
       <c r="C119" t="n">
-        <v>8.753216409689676</v>
+        <v>7.761611343307508</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
@@ -2111,10 +2111,10 @@
         <v>44078</v>
       </c>
       <c r="B120" t="n">
-        <v>57.34570427411356</v>
+        <v>58.63252438775155</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42569607729433</v>
+        <v>8.249820129650303</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -2125,10 +2125,10 @@
         <v>44085</v>
       </c>
       <c r="B121" t="n">
-        <v>56.69215247502772</v>
+        <v>57.80105951051468</v>
       </c>
       <c r="C121" t="n">
-        <v>12.25858369384969</v>
+        <v>7.945331641079631</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -2139,10 +2139,10 @@
         <v>44092</v>
       </c>
       <c r="B122" t="n">
-        <v>45.17254680195995</v>
+        <v>45.55859619058125</v>
       </c>
       <c r="C122" t="n">
-        <v>7.703272592369118</v>
+        <v>4.525334438735219</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
@@ -2153,10 +2153,10 @@
         <v>44099</v>
       </c>
       <c r="B123" t="n">
-        <v>45.36161143665908</v>
+        <v>45.61152531178644</v>
       </c>
       <c r="C123" t="n">
-        <v>7.969833115571115</v>
+        <v>4.770477176016127</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -2167,10 +2167,10 @@
         <v>44106</v>
       </c>
       <c r="B124" t="n">
-        <v>45.82379206794894</v>
+        <v>45.8370735712865</v>
       </c>
       <c r="C124" t="n">
-        <v>8.506329660503503</v>
+        <v>4.927968465212317</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
@@ -2181,10 +2181,10 @@
         <v>44113</v>
       </c>
       <c r="B125" t="n">
-        <v>45.28657061225613</v>
+        <v>45.7974811317521</v>
       </c>
       <c r="C125" t="n">
-        <v>8.318392765403777</v>
+        <v>4.48580317918293</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
@@ -2195,10 +2195,10 @@
         <v>44120</v>
       </c>
       <c r="B126" t="n">
-        <v>44.98938584156509</v>
+        <v>45.67547832386293</v>
       </c>
       <c r="C126" t="n">
-        <v>8.223560858173814</v>
+        <v>4.582226702315373</v>
       </c>
       <c r="D126" t="n">
         <v>1</v>
@@ -2209,10 +2209,10 @@
         <v>44127</v>
       </c>
       <c r="B127" t="n">
-        <v>45.28657619648991</v>
+        <v>46.18792348230037</v>
       </c>
       <c r="C127" t="n">
-        <v>7.928192388414834</v>
+        <v>4.186680199305246</v>
       </c>
       <c r="D127" t="n">
         <v>1</v>
@@ -2223,10 +2223,10 @@
         <v>44134</v>
       </c>
       <c r="B128" t="n">
-        <v>45.31484249736342</v>
+        <v>46.16566360237136</v>
       </c>
       <c r="C128" t="n">
-        <v>7.985031702740584</v>
+        <v>4.3758889211455</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
@@ -2237,10 +2237,10 @@
         <v>44141</v>
       </c>
       <c r="B129" t="n">
-        <v>43.15947493744378</v>
+        <v>44.33421786295312</v>
       </c>
       <c r="C129" t="n">
-        <v>8.362860914079596</v>
+        <v>5.266491097378092</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -2251,10 +2251,10 @@
         <v>44148</v>
       </c>
       <c r="B130" t="n">
-        <v>42.3443549404862</v>
+        <v>42.63991536315902</v>
       </c>
       <c r="C130" t="n">
-        <v>7.774911260250704</v>
+        <v>4.091003317297769</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
@@ -2265,10 +2265,10 @@
         <v>44155</v>
       </c>
       <c r="B131" t="n">
-        <v>42.3639174534477</v>
+        <v>43.34925507108407</v>
       </c>
       <c r="C131" t="n">
-        <v>7.57276569410865</v>
+        <v>4.334594021530878</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -2279,10 +2279,10 @@
         <v>44162</v>
       </c>
       <c r="B132" t="n">
-        <v>41.70255997997168</v>
+        <v>42.49569682893146</v>
       </c>
       <c r="C132" t="n">
-        <v>8.044148252464911</v>
+        <v>4.881035055239643</v>
       </c>
       <c r="D132" t="n">
         <v>1</v>
@@ -2293,10 +2293,10 @@
         <v>44169</v>
       </c>
       <c r="B133" t="n">
-        <v>42.85012212129703</v>
+        <v>43.83007420460106</v>
       </c>
       <c r="C133" t="n">
-        <v>6.038808360174212</v>
+        <v>2.673007891342055</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
@@ -2307,10 +2307,10 @@
         <v>44176</v>
       </c>
       <c r="B134" t="n">
-        <v>43.64465352108278</v>
+        <v>45.01359227198731</v>
       </c>
       <c r="C134" t="n">
-        <v>5.87581127988485</v>
+        <v>2.641658884649497</v>
       </c>
       <c r="D134" t="n">
         <v>1</v>
@@ -2321,10 +2321,10 @@
         <v>44183</v>
       </c>
       <c r="B135" t="n">
-        <v>43.6589230734781</v>
+        <v>45.03895837570883</v>
       </c>
       <c r="C135" t="n">
-        <v>6.095282386789306</v>
+        <v>2.845355867146544</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
@@ -2335,10 +2335,10 @@
         <v>44190</v>
       </c>
       <c r="B136" t="n">
-        <v>43.88751705823435</v>
+        <v>44.8469070341587</v>
       </c>
       <c r="C136" t="n">
-        <v>6.106741640906462</v>
+        <v>3.329671551290705</v>
       </c>
       <c r="D136" t="n">
         <v>1</v>
@@ -2349,10 +2349,10 @@
         <v>44197</v>
       </c>
       <c r="B137" t="n">
-        <v>43.22430688327665</v>
+        <v>43.71929739466634</v>
       </c>
       <c r="C137" t="n">
-        <v>5.465600416323465</v>
+        <v>2.644798969301027</v>
       </c>
       <c r="D137" t="n">
         <v>1</v>
@@ -2363,10 +2363,10 @@
         <v>44204</v>
       </c>
       <c r="B138" t="n">
-        <v>42.57520010857399</v>
+        <v>43.83768388538419</v>
       </c>
       <c r="C138" t="n">
-        <v>5.41824608709692</v>
+        <v>2.955217684644416</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -2377,10 +2377,10 @@
         <v>44211</v>
       </c>
       <c r="B139" t="n">
-        <v>42.05547414492074</v>
+        <v>43.64848765704772</v>
       </c>
       <c r="C139" t="n">
-        <v>5.388848950206574</v>
+        <v>3.13344405059925</v>
       </c>
       <c r="D139" t="n">
         <v>1</v>
@@ -2391,10 +2391,10 @@
         <v>44218</v>
       </c>
       <c r="B140" t="n">
-        <v>42.03679617917357</v>
+        <v>43.7082965492223</v>
       </c>
       <c r="C140" t="n">
-        <v>5.420969415617492</v>
+        <v>3.249130367339751</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
@@ -2405,10 +2405,10 @@
         <v>44225</v>
       </c>
       <c r="B141" t="n">
-        <v>42.33013324876316</v>
+        <v>44.19642705534408</v>
       </c>
       <c r="C141" t="n">
-        <v>5.719544913314467</v>
+        <v>3.473570858767236</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
@@ -2419,10 +2419,10 @@
         <v>44232</v>
       </c>
       <c r="B142" t="n">
-        <v>41.85753480233</v>
+        <v>43.55446995102162</v>
       </c>
       <c r="C142" t="n">
-        <v>6.221657321021863</v>
+        <v>3.506020975168569</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
@@ -2433,10 +2433,10 @@
         <v>44239</v>
       </c>
       <c r="B143" t="n">
-        <v>41.5132597211334</v>
+        <v>43.39899314649642</v>
       </c>
       <c r="C143" t="n">
-        <v>6.376178870727035</v>
+        <v>3.557955120335227</v>
       </c>
       <c r="D143" t="n">
         <v>1</v>
@@ -2447,10 +2447,10 @@
         <v>44246</v>
       </c>
       <c r="B144" t="n">
-        <v>41.43011625749114</v>
+        <v>42.15903899589643</v>
       </c>
       <c r="C144" t="n">
-        <v>7.716542576966597</v>
+        <v>4.112749430177535</v>
       </c>
       <c r="D144" t="n">
         <v>1</v>
@@ -2461,10 +2461,10 @@
         <v>44253</v>
       </c>
       <c r="B145" t="n">
-        <v>42.5515621897412</v>
+        <v>43.58438571255218</v>
       </c>
       <c r="C145" t="n">
-        <v>7.461990628291482</v>
+        <v>3.781164145004823</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
@@ -2475,10 +2475,10 @@
         <v>44260</v>
       </c>
       <c r="B146" t="n">
-        <v>57.86732109639396</v>
+        <v>56.90102086681589</v>
       </c>
       <c r="C146" t="n">
-        <v>16.9788570777977</v>
+        <v>8.359596979884577</v>
       </c>
       <c r="D146" t="n">
         <v>1</v>
@@ -2489,10 +2489,10 @@
         <v>44267</v>
       </c>
       <c r="B147" t="n">
-        <v>58.1707982069472</v>
+        <v>56.74028026102915</v>
       </c>
       <c r="C147" t="n">
-        <v>17.65258399295822</v>
+        <v>8.051078884380281</v>
       </c>
       <c r="D147" t="n">
         <v>1</v>
@@ -2503,10 +2503,10 @@
         <v>44274</v>
       </c>
       <c r="B148" t="n">
-        <v>57.76930068756989</v>
+        <v>56.71334072236377</v>
       </c>
       <c r="C148" t="n">
-        <v>15.97820416753716</v>
+        <v>7.680553666408795</v>
       </c>
       <c r="D148" t="n">
         <v>1</v>
@@ -2517,10 +2517,10 @@
         <v>44281</v>
       </c>
       <c r="B149" t="n">
-        <v>58.44966279725288</v>
+        <v>44.76134729745655</v>
       </c>
       <c r="C149" t="n">
-        <v>17.22813121741437</v>
+        <v>4.131856290273568</v>
       </c>
       <c r="D149" t="n">
         <v>1</v>
@@ -2531,10 +2531,10 @@
         <v>44288</v>
       </c>
       <c r="B150" t="n">
-        <v>42.59251141628309</v>
+        <v>44.43433443177414</v>
       </c>
       <c r="C150" t="n">
-        <v>7.688068845480044</v>
+        <v>3.965293027129098</v>
       </c>
       <c r="D150" t="n">
         <v>1</v>
@@ -2545,10 +2545,10 @@
         <v>44295</v>
       </c>
       <c r="B151" t="n">
-        <v>41.68234391217651</v>
+        <v>44.71105667994434</v>
       </c>
       <c r="C151" t="n">
-        <v>6.658065076785889</v>
+        <v>3.720111211072981</v>
       </c>
       <c r="D151" t="n">
         <v>1</v>
@@ -2559,10 +2559,10 @@
         <v>44302</v>
       </c>
       <c r="B152" t="n">
-        <v>41.75576414919698</v>
+        <v>44.69978260477593</v>
       </c>
       <c r="C152" t="n">
-        <v>6.483475436412252</v>
+        <v>3.556682137832939</v>
       </c>
       <c r="D152" t="n">
         <v>1</v>
@@ -2573,10 +2573,10 @@
         <v>44309</v>
       </c>
       <c r="B153" t="n">
-        <v>41.80493403440158</v>
+        <v>45.24095414796694</v>
       </c>
       <c r="C153" t="n">
-        <v>5.929833191941282</v>
+        <v>3.464856545805526</v>
       </c>
       <c r="D153" t="n">
         <v>1</v>
@@ -2587,10 +2587,10 @@
         <v>44316</v>
       </c>
       <c r="B154" t="n">
-        <v>40.78534814710042</v>
+        <v>43.89818755716712</v>
       </c>
       <c r="C154" t="n">
-        <v>6.128839056582609</v>
+        <v>3.8852209060284</v>
       </c>
       <c r="D154" t="n">
         <v>1</v>
@@ -2601,10 +2601,10 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>41.30928326526213</v>
+        <v>43.90329648481506</v>
       </c>
       <c r="C155" t="n">
-        <v>8.527048859626561</v>
+        <v>5.903228574850716</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
@@ -2615,10 +2615,10 @@
         <v>44330</v>
       </c>
       <c r="B156" t="n">
-        <v>42.01671442734735</v>
+        <v>44.63742790110168</v>
       </c>
       <c r="C156" t="n">
-        <v>8.606972995404014</v>
+        <v>6.001646853277878</v>
       </c>
       <c r="D156" t="n">
         <v>1</v>
@@ -2629,10 +2629,10 @@
         <v>44337</v>
       </c>
       <c r="B157" t="n">
-        <v>42.07303100849736</v>
+        <v>44.52444363595623</v>
       </c>
       <c r="C157" t="n">
-        <v>8.646139487860237</v>
+        <v>5.938032300794399</v>
       </c>
       <c r="D157" t="n">
         <v>1</v>
@@ -2643,10 +2643,10 @@
         <v>44344</v>
       </c>
       <c r="B158" t="n">
-        <v>41.4732189859837</v>
+        <v>43.79167894754368</v>
       </c>
       <c r="C158" t="n">
-        <v>8.764331545754986</v>
+        <v>5.92793022179573</v>
       </c>
       <c r="D158" t="n">
         <v>1</v>
@@ -2657,10 +2657,10 @@
         <v>44351</v>
       </c>
       <c r="B159" t="n">
-        <v>41.3007752588266</v>
+        <v>43.79669135011667</v>
       </c>
       <c r="C159" t="n">
-        <v>8.866106750667129</v>
+        <v>5.803712044904284</v>
       </c>
       <c r="D159" t="n">
         <v>1</v>
@@ -2671,10 +2671,10 @@
         <v>44358</v>
       </c>
       <c r="B160" t="n">
-        <v>41.83175745851702</v>
+        <v>44.47064806479509</v>
       </c>
       <c r="C160" t="n">
-        <v>10.52257795479544</v>
+        <v>6.926037958523946</v>
       </c>
       <c r="D160" t="n">
         <v>1</v>
@@ -2685,10 +2685,10 @@
         <v>44365</v>
       </c>
       <c r="B161" t="n">
-        <v>40.86692946579414</v>
+        <v>43.28019545798701</v>
       </c>
       <c r="C161" t="n">
-        <v>9.390059364920909</v>
+        <v>5.747830974558425</v>
       </c>
       <c r="D161" t="n">
         <v>1</v>
@@ -2699,10 +2699,10 @@
         <v>44372</v>
       </c>
       <c r="B162" t="n">
-        <v>40.41974816314581</v>
+        <v>43.4696031295836</v>
       </c>
       <c r="C162" t="n">
-        <v>7.866176903200611</v>
+        <v>4.683327088539834</v>
       </c>
       <c r="D162" t="n">
         <v>1</v>
@@ -2713,10 +2713,10 @@
         <v>44379</v>
       </c>
       <c r="B163" t="n">
-        <v>40.30520243774121</v>
+        <v>43.53423379366282</v>
       </c>
       <c r="C163" t="n">
-        <v>7.773426631660141</v>
+        <v>4.858129452067684</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
@@ -2727,10 +2727,10 @@
         <v>44386</v>
       </c>
       <c r="B164" t="n">
-        <v>40.19994999273521</v>
+        <v>43.28423850459037</v>
       </c>
       <c r="C164" t="n">
-        <v>7.929284447340722</v>
+        <v>5.101540528365708</v>
       </c>
       <c r="D164" t="n">
         <v>1</v>
@@ -2741,10 +2741,10 @@
         <v>44393</v>
       </c>
       <c r="B165" t="n">
-        <v>38.91276027294199</v>
+        <v>41.52768800980851</v>
       </c>
       <c r="C165" t="n">
-        <v>3.771876808796873</v>
+        <v>4.187631726460739</v>
       </c>
       <c r="D165" t="n">
         <v>1</v>
@@ -2755,10 +2755,10 @@
         <v>44400</v>
       </c>
       <c r="B166" t="n">
-        <v>39.33640113034733</v>
+        <v>41.83585305000681</v>
       </c>
       <c r="C166" t="n">
-        <v>4.111114951593649</v>
+        <v>3.808313426583676</v>
       </c>
       <c r="D166" t="n">
         <v>1</v>
@@ -2769,10 +2769,10 @@
         <v>44407</v>
       </c>
       <c r="B167" t="n">
-        <v>39.33584432627231</v>
+        <v>41.15683945740938</v>
       </c>
       <c r="C167" t="n">
-        <v>4.89018522559587</v>
+        <v>3.434326393815046</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
@@ -2783,10 +2783,10 @@
         <v>44414</v>
       </c>
       <c r="B168" t="n">
-        <v>41.91350085459056</v>
+        <v>44.28812580297872</v>
       </c>
       <c r="C168" t="n">
-        <v>7.271875797929265</v>
+        <v>6.628701709788226</v>
       </c>
       <c r="D168" t="n">
         <v>1</v>
@@ -2797,10 +2797,10 @@
         <v>44421</v>
       </c>
       <c r="B169" t="n">
-        <v>40.92185540194788</v>
+        <v>43.47105490849808</v>
       </c>
       <c r="C169" t="n">
-        <v>6.578997385282447</v>
+        <v>6.165957648770001</v>
       </c>
       <c r="D169" t="n">
         <v>1</v>
@@ -2811,10 +2811,10 @@
         <v>44428</v>
       </c>
       <c r="B170" t="n">
-        <v>40.80722748405027</v>
+        <v>43.57391522032051</v>
       </c>
       <c r="C170" t="n">
-        <v>6.441417255924025</v>
+        <v>6.307214103617934</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
@@ -2825,10 +2825,10 @@
         <v>44435</v>
       </c>
       <c r="B171" t="n">
-        <v>40.62067771581937</v>
+        <v>43.67364726638922</v>
       </c>
       <c r="C171" t="n">
-        <v>6.252780444854775</v>
+        <v>6.29664412947528</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
@@ -2839,10 +2839,10 @@
         <v>44442</v>
       </c>
       <c r="B172" t="n">
-        <v>40.6021622830953</v>
+        <v>43.66087444748658</v>
       </c>
       <c r="C172" t="n">
-        <v>5.243683725186632</v>
+        <v>5.135873024037758</v>
       </c>
       <c r="D172" t="n">
         <v>1</v>
@@ -2853,10 +2853,10 @@
         <v>44449</v>
       </c>
       <c r="B173" t="n">
-        <v>40.1040332584955</v>
+        <v>43.28685444865821</v>
       </c>
       <c r="C173" t="n">
-        <v>5.066254473788141</v>
+        <v>5.243434664828102</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
@@ -2867,10 +2867,10 @@
         <v>44456</v>
       </c>
       <c r="B174" t="n">
-        <v>40.23343458710474</v>
+        <v>43.25877266112851</v>
       </c>
       <c r="C174" t="n">
-        <v>4.980986269062932</v>
+        <v>5.228654683143936</v>
       </c>
       <c r="D174" t="n">
         <v>1</v>
@@ -2881,10 +2881,10 @@
         <v>44463</v>
       </c>
       <c r="B175" t="n">
-        <v>39.57961128087013</v>
+        <v>43.11640275225034</v>
       </c>
       <c r="C175" t="n">
-        <v>4.382932671355589</v>
+        <v>5.205313814513397</v>
       </c>
       <c r="D175" t="n">
         <v>1</v>
@@ -2895,10 +2895,10 @@
         <v>44470</v>
       </c>
       <c r="B176" t="n">
-        <v>39.74931827538929</v>
+        <v>43.28919330254124</v>
       </c>
       <c r="C176" t="n">
-        <v>4.455977914571316</v>
+        <v>5.154450420694414</v>
       </c>
       <c r="D176" t="n">
         <v>1</v>
@@ -2909,10 +2909,10 @@
         <v>44477</v>
       </c>
       <c r="B177" t="n">
-        <v>40.19647516097248</v>
+        <v>43.77954616496957</v>
       </c>
       <c r="C177" t="n">
-        <v>4.691736108034447</v>
+        <v>5.467959227338456</v>
       </c>
       <c r="D177" t="n">
         <v>1</v>
@@ -2923,10 +2923,10 @@
         <v>44484</v>
       </c>
       <c r="B178" t="n">
-        <v>39.95005212489891</v>
+        <v>43.59923367091375</v>
       </c>
       <c r="C178" t="n">
-        <v>4.664048100040475</v>
+        <v>5.440029801215663</v>
       </c>
       <c r="D178" t="n">
         <v>1</v>
@@ -2937,10 +2937,10 @@
         <v>44491</v>
       </c>
       <c r="B179" t="n">
-        <v>39.81478592394831</v>
+        <v>43.27847366245225</v>
       </c>
       <c r="C179" t="n">
-        <v>4.480523045129611</v>
+        <v>5.157509733377107</v>
       </c>
       <c r="D179" t="n">
         <v>1</v>
@@ -2951,10 +2951,10 @@
         <v>44498</v>
       </c>
       <c r="B180" t="n">
-        <v>40.75685387365937</v>
+        <v>44.45297569091957</v>
       </c>
       <c r="C180" t="n">
-        <v>5.884709086098613</v>
+        <v>5.632632242853172</v>
       </c>
       <c r="D180" t="n">
         <v>1</v>
@@ -2965,10 +2965,10 @@
         <v>44505</v>
       </c>
       <c r="B181" t="n">
-        <v>40.71308561595931</v>
+        <v>44.06747116357307</v>
       </c>
       <c r="C181" t="n">
-        <v>5.444754207425872</v>
+        <v>5.201159298619034</v>
       </c>
       <c r="D181" t="n">
         <v>1</v>
@@ -2979,10 +2979,10 @@
         <v>44512</v>
       </c>
       <c r="B182" t="n">
-        <v>41.09426646131337</v>
+        <v>44.10812073656673</v>
       </c>
       <c r="C182" t="n">
-        <v>4.914583238716098</v>
+        <v>4.923702068143386</v>
       </c>
       <c r="D182" t="n">
         <v>1</v>
@@ -2993,10 +2993,10 @@
         <v>44519</v>
       </c>
       <c r="B183" t="n">
-        <v>40.22206423535034</v>
+        <v>44.4599643524177</v>
       </c>
       <c r="C183" t="n">
-        <v>4.393538259032311</v>
+        <v>4.352819229136812</v>
       </c>
       <c r="D183" t="n">
         <v>1</v>
@@ -3007,10 +3007,10 @@
         <v>44526</v>
       </c>
       <c r="B184" t="n">
-        <v>40.66230435964393</v>
+        <v>45.56524433663259</v>
       </c>
       <c r="C184" t="n">
-        <v>4.315822709509722</v>
+        <v>4.898162805863648</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
@@ -3021,10 +3021,10 @@
         <v>44533</v>
       </c>
       <c r="B185" t="n">
-        <v>40.93702183667529</v>
+        <v>46.68180789444634</v>
       </c>
       <c r="C185" t="n">
-        <v>4.40010810828332</v>
+        <v>5.630872930468747</v>
       </c>
       <c r="D185" t="n">
         <v>1</v>
@@ -3035,10 +3035,10 @@
         <v>44540</v>
       </c>
       <c r="B186" t="n">
-        <v>40.83561988184007</v>
+        <v>46.24748020827056</v>
       </c>
       <c r="C186" t="n">
-        <v>4.630130038589687</v>
+        <v>5.527607358678067</v>
       </c>
       <c r="D186" t="n">
         <v>1</v>
@@ -3049,10 +3049,10 @@
         <v>44547</v>
       </c>
       <c r="B187" t="n">
-        <v>41.07239684170172</v>
+        <v>46.68616771281355</v>
       </c>
       <c r="C187" t="n">
-        <v>4.700395289347314</v>
+        <v>5.328150152980733</v>
       </c>
       <c r="D187" t="n">
         <v>1</v>
@@ -3063,10 +3063,10 @@
         <v>44554</v>
       </c>
       <c r="B188" t="n">
-        <v>41.47935519268174</v>
+        <v>47.76049183973089</v>
       </c>
       <c r="C188" t="n">
-        <v>4.605588105080701</v>
+        <v>5.668514616401576</v>
       </c>
       <c r="D188" t="n">
         <v>1</v>
@@ -3077,10 +3077,10 @@
         <v>44561</v>
       </c>
       <c r="B189" t="n">
-        <v>45.56540499339525</v>
+        <v>49.45348989563976</v>
       </c>
       <c r="C189" t="n">
-        <v>6.19695220089786</v>
+        <v>8.306100877764216</v>
       </c>
       <c r="D189" t="n">
         <v>1</v>
@@ -3091,10 +3091,10 @@
         <v>44568</v>
       </c>
       <c r="B190" t="n">
-        <v>45.46505390231074</v>
+        <v>48.13853169294047</v>
       </c>
       <c r="C190" t="n">
-        <v>6.57169902645612</v>
+        <v>7.016070901248602</v>
       </c>
       <c r="D190" t="n">
         <v>1</v>
@@ -3105,10 +3105,10 @@
         <v>44575</v>
       </c>
       <c r="B191" t="n">
-        <v>45.00607753957473</v>
+        <v>47.67042538504213</v>
       </c>
       <c r="C191" t="n">
-        <v>6.295955446800022</v>
+        <v>6.379512291820393</v>
       </c>
       <c r="D191" t="n">
         <v>1</v>
@@ -3119,10 +3119,10 @@
         <v>44582</v>
       </c>
       <c r="B192" t="n">
-        <v>44.97774764562823</v>
+        <v>47.873703932527</v>
       </c>
       <c r="C192" t="n">
-        <v>5.700933919830801</v>
+        <v>6.121950280213042</v>
       </c>
       <c r="D192" t="n">
         <v>1</v>
@@ -3133,10 +3133,10 @@
         <v>44589</v>
       </c>
       <c r="B193" t="n">
-        <v>45.42010364369551</v>
+        <v>47.7836399221628</v>
       </c>
       <c r="C193" t="n">
-        <v>5.352047534764897</v>
+        <v>5.858032382338648</v>
       </c>
       <c r="D193" t="n">
         <v>1</v>
@@ -3147,10 +3147,10 @@
         <v>44596</v>
       </c>
       <c r="B194" t="n">
-        <v>44.7990929131754</v>
+        <v>47.40735485691881</v>
       </c>
       <c r="C194" t="n">
-        <v>5.364076383949699</v>
+        <v>5.573620680306549</v>
       </c>
       <c r="D194" t="n">
         <v>1</v>
@@ -3161,10 +3161,10 @@
         <v>44603</v>
       </c>
       <c r="B195" t="n">
-        <v>45.07944225150502</v>
+        <v>47.15756801018023</v>
       </c>
       <c r="C195" t="n">
-        <v>5.58141840416428</v>
+        <v>5.425437734257439</v>
       </c>
       <c r="D195" t="n">
         <v>1</v>
@@ -3175,10 +3175,10 @@
         <v>44610</v>
       </c>
       <c r="B196" t="n">
-        <v>44.71259362647749</v>
+        <v>46.54199000156794</v>
       </c>
       <c r="C196" t="n">
-        <v>5.576688511622211</v>
+        <v>5.338872419463297</v>
       </c>
       <c r="D196" t="n">
         <v>1</v>
@@ -3189,10 +3189,10 @@
         <v>44617</v>
       </c>
       <c r="B197" t="n">
-        <v>44.73610611879152</v>
+        <v>46.88801121640187</v>
       </c>
       <c r="C197" t="n">
-        <v>5.891167676253794</v>
+        <v>5.721506220330832</v>
       </c>
       <c r="D197" t="n">
         <v>1</v>
@@ -3203,10 +3203,10 @@
         <v>44624</v>
       </c>
       <c r="B198" t="n">
-        <v>44.4667401160053</v>
+        <v>47.30040373718588</v>
       </c>
       <c r="C198" t="n">
-        <v>5.673495076995651</v>
+        <v>5.573654188480142</v>
       </c>
       <c r="D198" t="n">
         <v>1</v>
@@ -3217,10 +3217,10 @@
         <v>44631</v>
       </c>
       <c r="B199" t="n">
-        <v>45.41666417106851</v>
+        <v>47.63151571025492</v>
       </c>
       <c r="C199" t="n">
-        <v>6.060828609526975</v>
+        <v>5.940666035053241</v>
       </c>
       <c r="D199" t="n">
         <v>1</v>
@@ -3231,10 +3231,10 @@
         <v>44638</v>
       </c>
       <c r="B200" t="n">
-        <v>45.96547256073171</v>
+        <v>47.15408702189799</v>
       </c>
       <c r="C200" t="n">
-        <v>6.864347624159837</v>
+        <v>5.151308098493262</v>
       </c>
       <c r="D200" t="n">
         <v>1</v>
@@ -3245,10 +3245,10 @@
         <v>44645</v>
       </c>
       <c r="B201" t="n">
-        <v>46.09986940878203</v>
+        <v>47.40835000588199</v>
       </c>
       <c r="C201" t="n">
-        <v>6.985223339203834</v>
+        <v>5.501591057727209</v>
       </c>
       <c r="D201" t="n">
         <v>1</v>
@@ -3259,10 +3259,10 @@
         <v>44652</v>
       </c>
       <c r="B202" t="n">
-        <v>46.40782550877649</v>
+        <v>47.74261570953763</v>
       </c>
       <c r="C202" t="n">
-        <v>7.134552018387161</v>
+        <v>6.233263095288219</v>
       </c>
       <c r="D202" t="n">
         <v>1</v>
@@ -3273,10 +3273,10 @@
         <v>44659</v>
       </c>
       <c r="B203" t="n">
-        <v>45.41805085151113</v>
+        <v>48.08200110834358</v>
       </c>
       <c r="C203" t="n">
-        <v>6.806876452880119</v>
+        <v>6.841514020228799</v>
       </c>
       <c r="D203" t="n">
         <v>1</v>
@@ -3287,10 +3287,10 @@
         <v>44666</v>
       </c>
       <c r="B204" t="n">
-        <v>45.1400382230926</v>
+        <v>47.63169882861602</v>
       </c>
       <c r="C204" t="n">
-        <v>6.922602056664656</v>
+        <v>6.517255142054967</v>
       </c>
       <c r="D204" t="n">
         <v>1</v>
@@ -3301,10 +3301,10 @@
         <v>44673</v>
       </c>
       <c r="B205" t="n">
-        <v>45.7585604910258</v>
+        <v>48.0416694806316</v>
       </c>
       <c r="C205" t="n">
-        <v>6.906397181744619</v>
+        <v>6.396229997130364</v>
       </c>
       <c r="D205" t="n">
         <v>1</v>
@@ -3315,10 +3315,10 @@
         <v>44680</v>
       </c>
       <c r="B206" t="n">
-        <v>45.92700423909428</v>
+        <v>48.31048748387787</v>
       </c>
       <c r="C206" t="n">
-        <v>7.028627938805986</v>
+        <v>6.54654870820767</v>
       </c>
       <c r="D206" t="n">
         <v>1</v>
@@ -3329,10 +3329,10 @@
         <v>44687</v>
       </c>
       <c r="B207" t="n">
-        <v>44.52036612667687</v>
+        <v>46.54895442057218</v>
       </c>
       <c r="C207" t="n">
-        <v>6.796833023330202</v>
+        <v>6.536072771173268</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
@@ -3343,10 +3343,10 @@
         <v>44694</v>
       </c>
       <c r="B208" t="n">
-        <v>44.31070589765174</v>
+        <v>46.75212824902038</v>
       </c>
       <c r="C208" t="n">
-        <v>6.873912701282659</v>
+        <v>6.652207806893673</v>
       </c>
       <c r="D208" t="n">
         <v>1</v>
@@ -3357,10 +3357,10 @@
         <v>44701</v>
       </c>
       <c r="B209" t="n">
-        <v>43.59844128692574</v>
+        <v>46.91802227860452</v>
       </c>
       <c r="C209" t="n">
-        <v>5.714966569753961</v>
+        <v>6.232155681759597</v>
       </c>
       <c r="D209" t="n">
         <v>1</v>
@@ -3371,10 +3371,10 @@
         <v>44708</v>
       </c>
       <c r="B210" t="n">
-        <v>43.64145170884077</v>
+        <v>46.5367947374911</v>
       </c>
       <c r="C210" t="n">
-        <v>5.706950980408384</v>
+        <v>5.5498883130772</v>
       </c>
       <c r="D210" t="n">
         <v>1</v>
@@ -3385,10 +3385,10 @@
         <v>44715</v>
       </c>
       <c r="B211" t="n">
-        <v>42.74353636278652</v>
+        <v>46.60359886607602</v>
       </c>
       <c r="C211" t="n">
-        <v>4.431699657044231</v>
+        <v>5.578615795984999</v>
       </c>
       <c r="D211" t="n">
         <v>1</v>
@@ -3399,10 +3399,10 @@
         <v>44722</v>
       </c>
       <c r="B212" t="n">
-        <v>42.89530167938486</v>
+        <v>46.50356527325599</v>
       </c>
       <c r="C212" t="n">
-        <v>4.542398917980673</v>
+        <v>5.767285049452944</v>
       </c>
       <c r="D212" t="n">
         <v>1</v>
@@ -3413,10 +3413,10 @@
         <v>44729</v>
       </c>
       <c r="B213" t="n">
-        <v>43.26540799056264</v>
+        <v>46.53721206768708</v>
       </c>
       <c r="C213" t="n">
-        <v>4.458354467404673</v>
+        <v>5.675343947778996</v>
       </c>
       <c r="D213" t="n">
         <v>1</v>
@@ -3427,10 +3427,10 @@
         <v>44736</v>
       </c>
       <c r="B214" t="n">
-        <v>42.2397803918748</v>
+        <v>46.36920711854442</v>
       </c>
       <c r="C214" t="n">
-        <v>3.768123870847117</v>
+        <v>5.854926993478049</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>44743</v>
       </c>
       <c r="B215" t="n">
-        <v>41.87617448382549</v>
+        <v>46.04977093591881</v>
       </c>
       <c r="C215" t="n">
-        <v>3.600681500614251</v>
+        <v>5.906803227374517</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -3455,10 +3455,10 @@
         <v>44750</v>
       </c>
       <c r="B216" t="n">
-        <v>41.76438660250255</v>
+        <v>45.91626393677387</v>
       </c>
       <c r="C216" t="n">
-        <v>4.02026979430264</v>
+        <v>6.194909735326408</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -3469,10 +3469,10 @@
         <v>44757</v>
       </c>
       <c r="B217" t="n">
-        <v>40.18287227112322</v>
+        <v>45.05999170539631</v>
       </c>
       <c r="C217" t="n">
-        <v>3.959506433574844</v>
+        <v>6.935531711200722</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>
@@ -3483,10 +3483,10 @@
         <v>44764</v>
       </c>
       <c r="B218" t="n">
-        <v>40.59929490794742</v>
+        <v>45.41599690741409</v>
       </c>
       <c r="C218" t="n">
-        <v>3.904531471275911</v>
+        <v>7.003076941058529</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -3497,10 +3497,10 @@
         <v>44771</v>
       </c>
       <c r="B219" t="n">
-        <v>39.94213314775244</v>
+        <v>44.65745569665287</v>
       </c>
       <c r="C219" t="n">
-        <v>3.2883809346557</v>
+        <v>6.101454683056544</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -3511,10 +3511,10 @@
         <v>44778</v>
       </c>
       <c r="B220" t="n">
-        <v>40.19187423118049</v>
+        <v>44.70193760500931</v>
       </c>
       <c r="C220" t="n">
-        <v>3.277257333979441</v>
+        <v>5.80685525238076</v>
       </c>
       <c r="D220" t="n">
         <v>0</v>
@@ -3525,10 +3525,10 @@
         <v>44785</v>
       </c>
       <c r="B221" t="n">
-        <v>40.88052450601096</v>
+        <v>44.93542574322357</v>
       </c>
       <c r="C221" t="n">
-        <v>3.602413516127328</v>
+        <v>5.898557533685719</v>
       </c>
       <c r="D221" t="n">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         <v>44792</v>
       </c>
       <c r="B222" t="n">
-        <v>40.90300432603749</v>
+        <v>44.49670180328261</v>
       </c>
       <c r="C222" t="n">
-        <v>3.952060980636391</v>
+        <v>5.570976140918748</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -3553,10 +3553,10 @@
         <v>44799</v>
       </c>
       <c r="B223" t="n">
-        <v>41.4397727993317</v>
+        <v>44.83540419696024</v>
       </c>
       <c r="C223" t="n">
-        <v>4.585215476571268</v>
+        <v>5.961307053099244</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -3567,10 +3567,10 @@
         <v>44806</v>
       </c>
       <c r="B224" t="n">
-        <v>41.43576738214366</v>
+        <v>44.637200145228</v>
       </c>
       <c r="C224" t="n">
-        <v>4.611692706068743</v>
+        <v>5.874720436311884</v>
       </c>
       <c r="D224" t="n">
         <v>0</v>
@@ -3581,10 +3581,10 @@
         <v>44813</v>
       </c>
       <c r="B225" t="n">
-        <v>41.3707106473963</v>
+        <v>44.4982136421302</v>
       </c>
       <c r="C225" t="n">
-        <v>5.113226544800028</v>
+        <v>5.85257413135353</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>44820</v>
       </c>
       <c r="B226" t="n">
-        <v>41.21469624466628</v>
+        <v>44.54208250184012</v>
       </c>
       <c r="C226" t="n">
-        <v>5.357712504118016</v>
+        <v>6.595952984385242</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -3609,10 +3609,10 @@
         <v>44827</v>
       </c>
       <c r="B227" t="n">
-        <v>41.69389878414185</v>
+        <v>44.97049114370441</v>
       </c>
       <c r="C227" t="n">
-        <v>6.559420900329334</v>
+        <v>6.836838109499849</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -3623,10 +3623,10 @@
         <v>44834</v>
       </c>
       <c r="B228" t="n">
-        <v>40.71630942667068</v>
+        <v>43.07725260277378</v>
       </c>
       <c r="C228" t="n">
-        <v>6.418462100493563</v>
+        <v>6.30065485321958</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -3637,10 +3637,10 @@
         <v>44841</v>
       </c>
       <c r="B229" t="n">
-        <v>40.57029083174658</v>
+        <v>42.84947429433466</v>
       </c>
       <c r="C229" t="n">
-        <v>6.465220300770187</v>
+        <v>6.170273244834935</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -3651,10 +3651,10 @@
         <v>44848</v>
       </c>
       <c r="B230" t="n">
-        <v>39.80320134455857</v>
+        <v>41.99242727876665</v>
       </c>
       <c r="C230" t="n">
-        <v>6.144741220287117</v>
+        <v>5.755104932683073</v>
       </c>
       <c r="D230" t="n">
         <v>0</v>
@@ -3665,10 +3665,10 @@
         <v>44855</v>
       </c>
       <c r="B231" t="n">
-        <v>40.37524636436935</v>
+        <v>42.23217104447718</v>
       </c>
       <c r="C231" t="n">
-        <v>5.643549905812135</v>
+        <v>5.852221470490589</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>44862</v>
       </c>
       <c r="B232" t="n">
-        <v>40.37897814014553</v>
+        <v>42.30243950579703</v>
       </c>
       <c r="C232" t="n">
-        <v>5.686680501307578</v>
+        <v>6.046228842353683</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
@@ -3693,10 +3693,10 @@
         <v>44869</v>
       </c>
       <c r="B233" t="n">
-        <v>39.2431141771814</v>
+        <v>42.00256967760638</v>
       </c>
       <c r="C233" t="n">
-        <v>4.907951087411104</v>
+        <v>5.565338076887103</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
@@ -3707,10 +3707,10 @@
         <v>44876</v>
       </c>
       <c r="B234" t="n">
-        <v>39.32402457781732</v>
+        <v>41.99728007635461</v>
       </c>
       <c r="C234" t="n">
-        <v>4.639531491914147</v>
+        <v>5.294817289235362</v>
       </c>
       <c r="D234" t="n">
         <v>0</v>
@@ -3721,10 +3721,10 @@
         <v>44883</v>
       </c>
       <c r="B235" t="n">
-        <v>39.12239375881443</v>
+        <v>42.27908388021084</v>
       </c>
       <c r="C235" t="n">
-        <v>4.227015180966641</v>
+        <v>5.0465106997736</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>44890</v>
       </c>
       <c r="B236" t="n">
-        <v>39.17023898056366</v>
+        <v>42.2856037946326</v>
       </c>
       <c r="C236" t="n">
-        <v>4.034993702408752</v>
+        <v>4.573227501099128</v>
       </c>
       <c r="D236" t="n">
         <v>0</v>
@@ -3749,10 +3749,10 @@
         <v>44897</v>
       </c>
       <c r="B237" t="n">
-        <v>39.41732853248951</v>
+        <v>42.75511535033337</v>
       </c>
       <c r="C237" t="n">
-        <v>3.649339890478362</v>
+        <v>4.807234074590053</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -3763,10 +3763,10 @@
         <v>44904</v>
       </c>
       <c r="B238" t="n">
-        <v>39.6664997019683</v>
+        <v>42.74972051794648</v>
       </c>
       <c r="C238" t="n">
-        <v>3.663738349185711</v>
+        <v>4.784192613534394</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         <v>44911</v>
       </c>
       <c r="B239" t="n">
-        <v>40.07859266379702</v>
+        <v>42.98255648888295</v>
       </c>
       <c r="C239" t="n">
-        <v>4.046801346525317</v>
+        <v>4.880279318583932</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>44918</v>
       </c>
       <c r="B240" t="n">
-        <v>40.67463334767535</v>
+        <v>42.17874628423797</v>
       </c>
       <c r="C240" t="n">
-        <v>5.089091491569322</v>
+        <v>4.064314929834722</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -3805,10 +3805,10 @@
         <v>44925</v>
       </c>
       <c r="B241" t="n">
-        <v>41.36640218929452</v>
+        <v>42.21091862800701</v>
       </c>
       <c r="C241" t="n">
-        <v>5.574808675225006</v>
+        <v>4.542648373023409</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
@@ -3819,10 +3819,10 @@
         <v>44932</v>
       </c>
       <c r="B242" t="n">
-        <v>41.63463641930494</v>
+        <v>42.54878730290357</v>
       </c>
       <c r="C242" t="n">
-        <v>5.530997766111384</v>
+        <v>5.040323476250208</v>
       </c>
       <c r="D242" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>44939</v>
       </c>
       <c r="B243" t="n">
-        <v>40.73120274317938</v>
+        <v>42.47153661256482</v>
       </c>
       <c r="C243" t="n">
-        <v>5.541356076332189</v>
+        <v>5.494347069610708</v>
       </c>
       <c r="D243" t="n">
         <v>0</v>
@@ -3847,10 +3847,10 @@
         <v>44946</v>
       </c>
       <c r="B244" t="n">
-        <v>40.90889110911871</v>
+        <v>42.03989822190147</v>
       </c>
       <c r="C244" t="n">
-        <v>5.164505544375109</v>
+        <v>4.28123390482096</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -3861,10 +3861,10 @@
         <v>44953</v>
       </c>
       <c r="B245" t="n">
-        <v>41.97018823825186</v>
+        <v>42.27770338271524</v>
       </c>
       <c r="C245" t="n">
-        <v>4.9776369567281</v>
+        <v>4.038856569181408</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -3875,10 +3875,10 @@
         <v>44960</v>
       </c>
       <c r="B246" t="n">
-        <v>42.36429460327353</v>
+        <v>42.30764853060209</v>
       </c>
       <c r="C246" t="n">
-        <v>4.774153510072898</v>
+        <v>4.074519572371559</v>
       </c>
       <c r="D246" t="n">
         <v>0</v>
@@ -3889,10 +3889,10 @@
         <v>44967</v>
       </c>
       <c r="B247" t="n">
-        <v>43.52881316743221</v>
+        <v>43.26826624499906</v>
       </c>
       <c r="C247" t="n">
-        <v>5.171188332493712</v>
+        <v>4.155883446473644</v>
       </c>
       <c r="D247" t="n">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>44974</v>
       </c>
       <c r="B248" t="n">
-        <v>43.45491485903616</v>
+        <v>42.73491855199648</v>
       </c>
       <c r="C248" t="n">
-        <v>4.913894615868977</v>
+        <v>3.223142669320412</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>44981</v>
       </c>
       <c r="B249" t="n">
-        <v>42.43666281759204</v>
+        <v>41.84797914305815</v>
       </c>
       <c r="C249" t="n">
-        <v>4.952134450562853</v>
+        <v>3.163891719760937</v>
       </c>
       <c r="D249" t="n">
         <v>0</v>
@@ -3931,10 +3931,10 @@
         <v>44988</v>
       </c>
       <c r="B250" t="n">
-        <v>63.57293464824418</v>
+        <v>41.97035040330699</v>
       </c>
       <c r="C250" t="n">
-        <v>16.44875898759942</v>
+        <v>3.498018161195668</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -3945,10 +3945,10 @@
         <v>44995</v>
       </c>
       <c r="B251" t="n">
-        <v>65.045429864144</v>
+        <v>41.77703086752516</v>
       </c>
       <c r="C251" t="n">
-        <v>16.75038710342783</v>
+        <v>3.342284848593601</v>
       </c>
       <c r="D251" t="n">
         <v>0</v>
@@ -3959,10 +3959,10 @@
         <v>45002</v>
       </c>
       <c r="B252" t="n">
-        <v>63.19522710547502</v>
+        <v>41.74933730174448</v>
       </c>
       <c r="C252" t="n">
-        <v>15.03612883786898</v>
+        <v>3.279293789570352</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
@@ -3973,10 +3973,10 @@
         <v>45009</v>
       </c>
       <c r="B253" t="n">
-        <v>62.3571250008084</v>
+        <v>41.54885180888914</v>
       </c>
       <c r="C253" t="n">
-        <v>14.14729233275101</v>
+        <v>2.317628787040008</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>45016</v>
       </c>
       <c r="B254" t="n">
-        <v>44.31416284637265</v>
+        <v>41.84489143652825</v>
       </c>
       <c r="C254" t="n">
-        <v>6.549851361604079</v>
+        <v>2.541471724341716</v>
       </c>
       <c r="D254" t="n">
         <v>0</v>
@@ -4001,10 +4001,10 @@
         <v>45023</v>
       </c>
       <c r="B255" t="n">
-        <v>44.52791593400062</v>
+        <v>42.61779070613076</v>
       </c>
       <c r="C255" t="n">
-        <v>6.000909576377936</v>
+        <v>3.099448761749836</v>
       </c>
       <c r="D255" t="n">
         <v>0</v>
@@ -4015,10 +4015,10 @@
         <v>45030</v>
       </c>
       <c r="B256" t="n">
-        <v>44.1374326921784</v>
+        <v>42.80240429249533</v>
       </c>
       <c r="C256" t="n">
-        <v>5.703299175911027</v>
+        <v>2.412749801160676</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -4029,10 +4029,10 @@
         <v>45037</v>
       </c>
       <c r="B257" t="n">
-        <v>44.56245021219279</v>
+        <v>43.18652155904715</v>
       </c>
       <c r="C257" t="n">
-        <v>5.616566648912593</v>
+        <v>2.390676968683523</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -4043,10 +4043,10 @@
         <v>45044</v>
       </c>
       <c r="B258" t="n">
-        <v>46.65401027530805</v>
+        <v>45.67364507363707</v>
       </c>
       <c r="C258" t="n">
-        <v>5.546469197850699</v>
+        <v>2.33371275510021</v>
       </c>
       <c r="D258" t="n">
         <v>0</v>
@@ -4057,10 +4057,10 @@
         <v>45051</v>
       </c>
       <c r="B259" t="n">
-        <v>62.56977080632314</v>
+        <v>45.65471278510734</v>
       </c>
       <c r="C259" t="n">
-        <v>13.86939098023802</v>
+        <v>2.021547684365143</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -4071,10 +4071,10 @@
         <v>45058</v>
       </c>
       <c r="B260" t="n">
-        <v>61.33809027762572</v>
+        <v>45.62908508213338</v>
       </c>
       <c r="C260" t="n">
-        <v>13.73658868994293</v>
+        <v>2.125515232936468</v>
       </c>
       <c r="D260" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>45065</v>
       </c>
       <c r="B261" t="n">
-        <v>44.63424283845322</v>
+        <v>44.85262146976606</v>
       </c>
       <c r="C261" t="n">
-        <v>3.815302708683051</v>
+        <v>3.869789372010412</v>
       </c>
       <c r="D261" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>45072</v>
       </c>
       <c r="B262" t="n">
-        <v>44.80905470224118</v>
+        <v>45.53921028240909</v>
       </c>
       <c r="C262" t="n">
-        <v>4.169609753729438</v>
+        <v>3.846612480821665</v>
       </c>
       <c r="D262" t="n">
         <v>0</v>
@@ -4113,10 +4113,10 @@
         <v>45079</v>
       </c>
       <c r="B263" t="n">
-        <v>44.73554470687875</v>
+        <v>45.43946439603754</v>
       </c>
       <c r="C263" t="n">
-        <v>4.170375987860007</v>
+        <v>3.653129313041004</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -4127,10 +4127,10 @@
         <v>45086</v>
       </c>
       <c r="B264" t="n">
-        <v>45.00364152362252</v>
+        <v>45.8729465497038</v>
       </c>
       <c r="C264" t="n">
-        <v>4.099328044187959</v>
+        <v>3.548538075408057</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         <v>45093</v>
       </c>
       <c r="B265" t="n">
-        <v>45.81674020361242</v>
+        <v>46.20749532284835</v>
       </c>
       <c r="C265" t="n">
-        <v>4.84846267312385</v>
+        <v>4.149500465939215</v>
       </c>
       <c r="D265" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>45100</v>
       </c>
       <c r="B266" t="n">
-        <v>44.74176070762019</v>
+        <v>46.48407866387105</v>
       </c>
       <c r="C266" t="n">
-        <v>4.74535015267473</v>
+        <v>3.866684975450941</v>
       </c>
       <c r="D266" t="n">
         <v>0</v>
@@ -4169,10 +4169,10 @@
         <v>45107</v>
       </c>
       <c r="B267" t="n">
-        <v>44.79370285042179</v>
+        <v>46.15678377628146</v>
       </c>
       <c r="C267" t="n">
-        <v>4.190952918720154</v>
+        <v>3.680061421865676</v>
       </c>
       <c r="D267" t="n">
         <v>0</v>
@@ -4183,10 +4183,10 @@
         <v>45114</v>
       </c>
       <c r="B268" t="n">
-        <v>44.26771240269814</v>
+        <v>46.2946784517589</v>
       </c>
       <c r="C268" t="n">
-        <v>4.195495545595668</v>
+        <v>3.529552467808307</v>
       </c>
       <c r="D268" t="n">
         <v>0</v>
@@ -4197,10 +4197,10 @@
         <v>45121</v>
       </c>
       <c r="B269" t="n">
-        <v>44.1282441808405</v>
+        <v>45.88894005014907</v>
       </c>
       <c r="C269" t="n">
-        <v>3.977012602736388</v>
+        <v>3.479287053080597</v>
       </c>
       <c r="D269" t="n">
         <v>0</v>
@@ -4211,10 +4211,10 @@
         <v>45128</v>
       </c>
       <c r="B270" t="n">
-        <v>43.82860870091866</v>
+        <v>45.38100282268431</v>
       </c>
       <c r="C270" t="n">
-        <v>3.768362208072188</v>
+        <v>3.273486971624142</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
@@ -4225,10 +4225,10 @@
         <v>45135</v>
       </c>
       <c r="B271" t="n">
-        <v>43.9431817634999</v>
+        <v>45.32193360888318</v>
       </c>
       <c r="C271" t="n">
-        <v>3.846517636804946</v>
+        <v>3.317088480335085</v>
       </c>
       <c r="D271" t="n">
         <v>0</v>
@@ -4239,10 +4239,10 @@
         <v>45142</v>
       </c>
       <c r="B272" t="n">
-        <v>43.97094679686632</v>
+        <v>45.68016890841432</v>
       </c>
       <c r="C272" t="n">
-        <v>3.745320670248944</v>
+        <v>3.200103041221442</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
@@ -4253,10 +4253,10 @@
         <v>45149</v>
       </c>
       <c r="B273" t="n">
-        <v>43.25796482399095</v>
+        <v>44.23419273549312</v>
       </c>
       <c r="C273" t="n">
-        <v>3.653770098387209</v>
+        <v>2.450413353584386</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -4267,10 +4267,10 @@
         <v>45156</v>
       </c>
       <c r="B274" t="n">
-        <v>43.49845676650947</v>
+        <v>43.80258868945456</v>
       </c>
       <c r="C274" t="n">
-        <v>3.877180878207419</v>
+        <v>2.31632445992835</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
@@ -4281,10 +4281,10 @@
         <v>45163</v>
       </c>
       <c r="B275" t="n">
-        <v>43.23441978227265</v>
+        <v>44.25191270524093</v>
       </c>
       <c r="C275" t="n">
-        <v>3.870076488223562</v>
+        <v>2.559945407297301</v>
       </c>
       <c r="D275" t="n">
         <v>0</v>
@@ -4295,10 +4295,10 @@
         <v>45170</v>
       </c>
       <c r="B276" t="n">
-        <v>44.24086393272603</v>
+        <v>44.29623713771986</v>
       </c>
       <c r="C276" t="n">
-        <v>3.178798862474719</v>
+        <v>2.15760007685146</v>
       </c>
       <c r="D276" t="n">
         <v>0</v>
@@ -4309,10 +4309,10 @@
         <v>45177</v>
       </c>
       <c r="B277" t="n">
-        <v>43.07687919802307</v>
+        <v>44.26735135388711</v>
       </c>
       <c r="C277" t="n">
-        <v>3.805708119119142</v>
+        <v>2.413121451259435</v>
       </c>
       <c r="D277" t="n">
         <v>0</v>
@@ -4323,10 +4323,10 @@
         <v>45184</v>
       </c>
       <c r="B278" t="n">
-        <v>41.18971350568432</v>
+        <v>42.7807399967671</v>
       </c>
       <c r="C278" t="n">
-        <v>3.125339370148291</v>
+        <v>1.599967681692134</v>
       </c>
       <c r="D278" t="n">
         <v>0</v>
@@ -4337,10 +4337,10 @@
         <v>45191</v>
       </c>
       <c r="B279" t="n">
-        <v>37.91331041111662</v>
+        <v>42.77564090056404</v>
       </c>
       <c r="C279" t="n">
-        <v>2.415833316073286</v>
+        <v>1.433189452348314</v>
       </c>
       <c r="D279" t="n">
         <v>0</v>
@@ -4351,10 +4351,10 @@
         <v>45198</v>
       </c>
       <c r="B280" t="n">
-        <v>38.79322743122349</v>
+        <v>42.79583131901229</v>
       </c>
       <c r="C280" t="n">
-        <v>2.963273989021884</v>
+        <v>1.608222416731879</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -4365,10 +4365,10 @@
         <v>45205</v>
       </c>
       <c r="B281" t="n">
-        <v>39.04039149044979</v>
+        <v>42.89022881382223</v>
       </c>
       <c r="C281" t="n">
-        <v>3.010937657974309</v>
+        <v>1.560499278993786</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -4379,10 +4379,10 @@
         <v>45212</v>
       </c>
       <c r="B282" t="n">
-        <v>39.19959736290587</v>
+        <v>43.32414876512934</v>
       </c>
       <c r="C282" t="n">
-        <v>2.805886859873185</v>
+        <v>1.455550075091492</v>
       </c>
       <c r="D282" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>45219</v>
       </c>
       <c r="B283" t="n">
-        <v>39.71710353448004</v>
+        <v>43.90964486404462</v>
       </c>
       <c r="C283" t="n">
-        <v>2.977404624284727</v>
+        <v>1.654489689401727</v>
       </c>
       <c r="D283" t="n">
         <v>0</v>
@@ -4407,10 +4407,10 @@
         <v>45226</v>
       </c>
       <c r="B284" t="n">
-        <v>38.76795771485365</v>
+        <v>42.1147518133354</v>
       </c>
       <c r="C284" t="n">
-        <v>2.47271537671496</v>
+        <v>1.242805453516178</v>
       </c>
       <c r="D284" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>45233</v>
       </c>
       <c r="B285" t="n">
-        <v>39.4831979788797</v>
+        <v>42.47854982385277</v>
       </c>
       <c r="C285" t="n">
-        <v>2.975739176618555</v>
+        <v>1.331813809039076</v>
       </c>
       <c r="D285" t="n">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         <v>45240</v>
       </c>
       <c r="B286" t="n">
-        <v>38.94496765005014</v>
+        <v>42.04533182316352</v>
       </c>
       <c r="C286" t="n">
-        <v>2.956043004427985</v>
+        <v>1.395836524647952</v>
       </c>
       <c r="D286" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>45247</v>
       </c>
       <c r="B287" t="n">
-        <v>39.03261508712831</v>
+        <v>40.40252896033144</v>
       </c>
       <c r="C287" t="n">
-        <v>3.352513001431222</v>
+        <v>1.640109109869688</v>
       </c>
       <c r="D287" t="n">
         <v>0</v>
@@ -4463,10 +4463,10 @@
         <v>45254</v>
       </c>
       <c r="B288" t="n">
-        <v>39.86838444733698</v>
+        <v>41.12636929789068</v>
       </c>
       <c r="C288" t="n">
-        <v>4.296077606509199</v>
+        <v>2.23345656200138</v>
       </c>
       <c r="D288" t="n">
         <v>0</v>
@@ -4477,10 +4477,10 @@
         <v>45261</v>
       </c>
       <c r="B289" t="n">
-        <v>40.21202820139292</v>
+        <v>41.56941446664253</v>
       </c>
       <c r="C289" t="n">
-        <v>4.377679419052098</v>
+        <v>2.331895563113487</v>
       </c>
       <c r="D289" t="n">
         <v>0</v>
@@ -4491,10 +4491,10 @@
         <v>45268</v>
       </c>
       <c r="B290" t="n">
-        <v>39.08310334873854</v>
+        <v>41.18662114639204</v>
       </c>
       <c r="C290" t="n">
-        <v>5.72272552177554</v>
+        <v>2.120389869906251</v>
       </c>
       <c r="D290" t="n">
         <v>0</v>
@@ -4505,10 +4505,10 @@
         <v>45275</v>
       </c>
       <c r="B291" t="n">
-        <v>36.38315290884202</v>
+        <v>40.79794276468559</v>
       </c>
       <c r="C291" t="n">
-        <v>3.360955902106507</v>
+        <v>2.093856302056432</v>
       </c>
       <c r="D291" t="n">
         <v>0</v>
@@ -4519,10 +4519,10 @@
         <v>45282</v>
       </c>
       <c r="B292" t="n">
-        <v>36.24316397241497</v>
+        <v>42.01218194809047</v>
       </c>
       <c r="C292" t="n">
-        <v>3.372268870396885</v>
+        <v>2.620931412100767</v>
       </c>
       <c r="D292" t="n">
         <v>0</v>
@@ -4533,10 +4533,10 @@
         <v>45289</v>
       </c>
       <c r="B293" t="n">
-        <v>36.06025226982057</v>
+        <v>42.63763593232795</v>
       </c>
       <c r="C293" t="n">
-        <v>3.195179620748576</v>
+        <v>3.098438486688268</v>
       </c>
       <c r="D293" t="n">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         <v>45296</v>
       </c>
       <c r="B294" t="n">
-        <v>35.88928337207371</v>
+        <v>41.86227537551139</v>
       </c>
       <c r="C294" t="n">
-        <v>3.232709701215029</v>
+        <v>2.948290975988749</v>
       </c>
       <c r="D294" t="n">
         <v>0</v>
@@ -4561,10 +4561,10 @@
         <v>45303</v>
       </c>
       <c r="B295" t="n">
-        <v>35.19170745786235</v>
+        <v>41.1944216691381</v>
       </c>
       <c r="C295" t="n">
-        <v>2.880865275710786</v>
+        <v>2.775957815776861</v>
       </c>
       <c r="D295" t="n">
         <v>0</v>
@@ -4575,10 +4575,10 @@
         <v>45310</v>
       </c>
       <c r="B296" t="n">
-        <v>34.37758830968803</v>
+        <v>40.39930075815069</v>
       </c>
       <c r="C296" t="n">
-        <v>3.017489078164144</v>
+        <v>2.296750350447038</v>
       </c>
       <c r="D296" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>45317</v>
       </c>
       <c r="B297" t="n">
-        <v>34.42357728589462</v>
+        <v>40.08883587580149</v>
       </c>
       <c r="C297" t="n">
-        <v>3.091444335278726</v>
+        <v>2.10257444475562</v>
       </c>
       <c r="D297" t="n">
         <v>0</v>
@@ -4603,10 +4603,10 @@
         <v>45324</v>
       </c>
       <c r="B298" t="n">
-        <v>35.29753383594836</v>
+        <v>40.55439282680942</v>
       </c>
       <c r="C298" t="n">
-        <v>3.075386081135661</v>
+        <v>2.064859885204744</v>
       </c>
       <c r="D298" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>45331</v>
       </c>
       <c r="B299" t="n">
-        <v>34.72071790503423</v>
+        <v>40.19907759202224</v>
       </c>
       <c r="C299" t="n">
-        <v>3.484004972276535</v>
+        <v>1.947169533486314</v>
       </c>
       <c r="D299" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>45338</v>
       </c>
       <c r="B300" t="n">
-        <v>39.84587733407415</v>
+        <v>46.63081077655792</v>
       </c>
       <c r="C300" t="n">
-        <v>6.248823699589638</v>
+        <v>6.284419592527711</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -4645,10 +4645,10 @@
         <v>45345</v>
       </c>
       <c r="B301" t="n">
-        <v>39.33438971494089</v>
+        <v>44.60872009038336</v>
       </c>
       <c r="C301" t="n">
-        <v>4.991021302037865</v>
+        <v>5.553339734527365</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -4659,10 +4659,10 @@
         <v>45352</v>
       </c>
       <c r="B302" t="n">
-        <v>38.70384580106165</v>
+        <v>44.0473120810067</v>
       </c>
       <c r="C302" t="n">
-        <v>4.303560029162313</v>
+        <v>3.830331134909542</v>
       </c>
       <c r="D302" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>45359</v>
       </c>
       <c r="B303" t="n">
-        <v>38.65394612851525</v>
+        <v>44.14150849584917</v>
       </c>
       <c r="C303" t="n">
-        <v>4.379981434043368</v>
+        <v>3.934261543779763</v>
       </c>
       <c r="D303" t="n">
         <v>0</v>
@@ -4687,10 +4687,10 @@
         <v>45366</v>
       </c>
       <c r="B304" t="n">
-        <v>38.52184009637205</v>
+        <v>44.02497645300436</v>
       </c>
       <c r="C304" t="n">
-        <v>3.759768262950604</v>
+        <v>3.182789904464146</v>
       </c>
       <c r="D304" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>45373</v>
       </c>
       <c r="B305" t="n">
-        <v>41.05389520038414</v>
+        <v>46.69052672203119</v>
       </c>
       <c r="C305" t="n">
-        <v>5.953955065353407</v>
+        <v>5.081382868587955</v>
       </c>
       <c r="D305" t="n">
         <v>0</v>
@@ -4715,10 +4715,10 @@
         <v>45380</v>
       </c>
       <c r="B306" t="n">
-        <v>40.72919913935858</v>
+        <v>46.69369534741001</v>
       </c>
       <c r="C306" t="n">
-        <v>5.884031022672723</v>
+        <v>5.384771095755548</v>
       </c>
       <c r="D306" t="n">
         <v>0</v>
@@ -4729,10 +4729,10 @@
         <v>45387</v>
       </c>
       <c r="B307" t="n">
-        <v>41.47967688504709</v>
+        <v>47.68005723815703</v>
       </c>
       <c r="C307" t="n">
-        <v>6.393065195722767</v>
+        <v>5.79875405303157</v>
       </c>
       <c r="D307" t="n">
         <v>0</v>
@@ -4743,10 +4743,10 @@
         <v>45394</v>
       </c>
       <c r="B308" t="n">
-        <v>41.7641141508196</v>
+        <v>48.1569637999491</v>
       </c>
       <c r="C308" t="n">
-        <v>6.622199125994251</v>
+        <v>6.44490511658658</v>
       </c>
       <c r="D308" t="n">
         <v>0</v>
@@ -4757,10 +4757,10 @@
         <v>45401</v>
       </c>
       <c r="B309" t="n">
-        <v>41.45707480337082</v>
+        <v>47.79723423921754</v>
       </c>
       <c r="C309" t="n">
-        <v>6.940820334702209</v>
+        <v>6.651984480291069</v>
       </c>
       <c r="D309" t="n">
         <v>0</v>
@@ -4771,10 +4771,10 @@
         <v>45408</v>
       </c>
       <c r="B310" t="n">
-        <v>41.72373221797216</v>
+        <v>48.38084765413865</v>
       </c>
       <c r="C310" t="n">
-        <v>7.191834811193599</v>
+        <v>7.893420923527321</v>
       </c>
       <c r="D310" t="n">
         <v>0</v>
@@ -4785,10 +4785,10 @@
         <v>45415</v>
       </c>
       <c r="B311" t="n">
-        <v>41.83103409631691</v>
+        <v>48.99152727790939</v>
       </c>
       <c r="C311" t="n">
-        <v>7.252061998410776</v>
+        <v>8.683162801498405</v>
       </c>
       <c r="D311" t="n">
         <v>0</v>
@@ -4799,10 +4799,10 @@
         <v>45422</v>
       </c>
       <c r="B312" t="n">
-        <v>41.77234743068556</v>
+        <v>48.66511607851632</v>
       </c>
       <c r="C312" t="n">
-        <v>7.685636933649731</v>
+        <v>9.129578799308717</v>
       </c>
       <c r="D312" t="n">
         <v>0</v>
@@ -4813,10 +4813,10 @@
         <v>45429</v>
       </c>
       <c r="B313" t="n">
-        <v>41.61355343104309</v>
+        <v>48.24530091866303</v>
       </c>
       <c r="C313" t="n">
-        <v>7.406204964728685</v>
+        <v>8.77075944685904</v>
       </c>
       <c r="D313" t="n">
         <v>0</v>
@@ -4827,10 +4827,10 @@
         <v>45436</v>
       </c>
       <c r="B314" t="n">
-        <v>40.97716690353374</v>
+        <v>48.65378558235815</v>
       </c>
       <c r="C314" t="n">
-        <v>7.57846805702479</v>
+        <v>9.14689906701685</v>
       </c>
       <c r="D314" t="n">
         <v>0</v>
@@ -4841,10 +4841,10 @@
         <v>45443</v>
       </c>
       <c r="B315" t="n">
-        <v>40.63229239195774</v>
+        <v>48.41699224833685</v>
       </c>
       <c r="C315" t="n">
-        <v>7.936406162820972</v>
+        <v>8.513074793831237</v>
       </c>
       <c r="D315" t="n">
         <v>0</v>
@@ -4855,10 +4855,10 @@
         <v>45450</v>
       </c>
       <c r="B316" t="n">
-        <v>41.33280952729749</v>
+        <v>49.23602391843193</v>
       </c>
       <c r="C316" t="n">
-        <v>8.624464223576311</v>
+        <v>9.332522442743594</v>
       </c>
       <c r="D316" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>45457</v>
       </c>
       <c r="B317" t="n">
-        <v>41.0983001282772</v>
+        <v>48.93213265585698</v>
       </c>
       <c r="C317" t="n">
-        <v>8.193946355886824</v>
+        <v>8.917221481543875</v>
       </c>
       <c r="D317" t="n">
         <v>0</v>
@@ -4883,10 +4883,10 @@
         <v>45464</v>
       </c>
       <c r="B318" t="n">
-        <v>41.53923202858133</v>
+        <v>48.91594156564741</v>
       </c>
       <c r="C318" t="n">
-        <v>8.418640245914231</v>
+        <v>9.01418747932828</v>
       </c>
       <c r="D318" t="n">
         <v>0</v>
@@ -4897,10 +4897,10 @@
         <v>45471</v>
       </c>
       <c r="B319" t="n">
-        <v>41.77339131918264</v>
+        <v>48.7706422686374</v>
       </c>
       <c r="C319" t="n">
-        <v>7.381267417605408</v>
+        <v>8.036625181018746</v>
       </c>
       <c r="D319" t="n">
         <v>0</v>
@@ -4911,10 +4911,10 @@
         <v>45478</v>
       </c>
       <c r="B320" t="n">
-        <v>41.29293308680934</v>
+        <v>49.02853982868837</v>
       </c>
       <c r="C320" t="n">
-        <v>7.827444041959984</v>
+        <v>8.637036755588269</v>
       </c>
       <c r="D320" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>45485</v>
       </c>
       <c r="B321" t="n">
-        <v>41.952000958853</v>
+        <v>49.4980538987179</v>
       </c>
       <c r="C321" t="n">
-        <v>8.34533610698797</v>
+        <v>8.880697219188688</v>
       </c>
       <c r="D321" t="n">
         <v>0</v>
@@ -4939,10 +4939,10 @@
         <v>45492</v>
       </c>
       <c r="B322" t="n">
-        <v>42.20498732228552</v>
+        <v>50.16341732447749</v>
       </c>
       <c r="C322" t="n">
-        <v>8.691496160015806</v>
+        <v>9.282779009344956</v>
       </c>
       <c r="D322" t="n">
         <v>0</v>
@@ -4953,10 +4953,10 @@
         <v>45499</v>
       </c>
       <c r="B323" t="n">
-        <v>42.16520502007183</v>
+        <v>50.28017839272326</v>
       </c>
       <c r="C323" t="n">
-        <v>8.763967457872168</v>
+        <v>9.559601023513457</v>
       </c>
       <c r="D323" t="n">
         <v>0</v>
@@ -4967,10 +4967,10 @@
         <v>45506</v>
       </c>
       <c r="B324" t="n">
-        <v>42.1210450146017</v>
+        <v>51.35255860548404</v>
       </c>
       <c r="C324" t="n">
-        <v>8.362074409813648</v>
+        <v>9.476759454975459</v>
       </c>
       <c r="D324" t="n">
         <v>0</v>
@@ -4981,10 +4981,10 @@
         <v>45513</v>
       </c>
       <c r="B325" t="n">
-        <v>42.20965337550383</v>
+        <v>51.17708733201489</v>
       </c>
       <c r="C325" t="n">
-        <v>8.469292683724527</v>
+        <v>9.187865344519741</v>
       </c>
       <c r="D325" t="n">
         <v>0</v>
@@ -4995,10 +4995,10 @@
         <v>45520</v>
       </c>
       <c r="B326" t="n">
-        <v>42.34577766444312</v>
+        <v>51.13562662280288</v>
       </c>
       <c r="C326" t="n">
-        <v>8.172815301422011</v>
+        <v>8.816164004649055</v>
       </c>
       <c r="D326" t="n">
         <v>0</v>
@@ -5009,10 +5009,10 @@
         <v>45527</v>
       </c>
       <c r="B327" t="n">
-        <v>42.66820923690559</v>
+        <v>49.81733525582121</v>
       </c>
       <c r="C327" t="n">
-        <v>8.128521648105357</v>
+        <v>8.44484730986683</v>
       </c>
       <c r="D327" t="n">
         <v>0</v>
@@ -5023,10 +5023,10 @@
         <v>45534</v>
       </c>
       <c r="B328" t="n">
-        <v>43.44909306264984</v>
+        <v>49.62213264467335</v>
       </c>
       <c r="C328" t="n">
-        <v>8.70806086315698</v>
+        <v>8.710830669174484</v>
       </c>
       <c r="D328" t="n">
         <v>0</v>
@@ -5037,10 +5037,10 @@
         <v>45541</v>
       </c>
       <c r="B329" t="n">
-        <v>42.66364964208077</v>
+        <v>48.78951146597174</v>
       </c>
       <c r="C329" t="n">
-        <v>8.356644099148069</v>
+        <v>8.414274893684862</v>
       </c>
       <c r="D329" t="n">
         <v>0</v>
@@ -5051,10 +5051,10 @@
         <v>45548</v>
       </c>
       <c r="B330" t="n">
-        <v>45.30922031077623</v>
+        <v>50.64764297196621</v>
       </c>
       <c r="C330" t="n">
-        <v>10.5633288233753</v>
+        <v>10.30549770008308</v>
       </c>
       <c r="D330" t="n">
         <v>0</v>
@@ -5065,10 +5065,10 @@
         <v>45555</v>
       </c>
       <c r="B331" t="n">
-        <v>44.9374945001484</v>
+        <v>50.51827859609094</v>
       </c>
       <c r="C331" t="n">
-        <v>10.36064111495442</v>
+        <v>10.08652981818091</v>
       </c>
       <c r="D331" t="n">
         <v>0</v>
@@ -5079,10 +5079,10 @@
         <v>45562</v>
       </c>
       <c r="B332" t="n">
-        <v>45.5558847057315</v>
+        <v>51.08341279125958</v>
       </c>
       <c r="C332" t="n">
-        <v>11.05580408337892</v>
+        <v>10.97335185163216</v>
       </c>
       <c r="D332" t="n">
         <v>0</v>
@@ -5093,10 +5093,10 @@
         <v>45569</v>
       </c>
       <c r="B333" t="n">
-        <v>45.65691912993866</v>
+        <v>51.09436722613271</v>
       </c>
       <c r="C333" t="n">
-        <v>11.37982701759268</v>
+        <v>11.0309655586512</v>
       </c>
       <c r="D333" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>45576</v>
       </c>
       <c r="B334" t="n">
-        <v>45.72549826553447</v>
+        <v>50.80646764022168</v>
       </c>
       <c r="C334" t="n">
-        <v>11.17462211522236</v>
+        <v>10.97095905115188</v>
       </c>
       <c r="D334" t="n">
         <v>0</v>
@@ -5121,10 +5121,10 @@
         <v>45583</v>
       </c>
       <c r="B335" t="n">
-        <v>45.12858791270902</v>
+        <v>51.0523331673047</v>
       </c>
       <c r="C335" t="n">
-        <v>8.877436165914544</v>
+        <v>9.768236713466372</v>
       </c>
       <c r="D335" t="n">
         <v>0</v>
@@ -5135,10 +5135,10 @@
         <v>45590</v>
       </c>
       <c r="B336" t="n">
-        <v>45.27321924982257</v>
+        <v>51.32591870197052</v>
       </c>
       <c r="C336" t="n">
-        <v>6.790305019047071</v>
+        <v>8.126198694269762</v>
       </c>
       <c r="D336" t="n">
         <v>0</v>
@@ -5149,10 +5149,10 @@
         <v>45597</v>
       </c>
       <c r="B337" t="n">
-        <v>44.89619068129144</v>
+        <v>51.28995896739019</v>
       </c>
       <c r="C337" t="n">
-        <v>5.822499851263446</v>
+        <v>7.176310029760972</v>
       </c>
       <c r="D337" t="n">
         <v>0</v>
@@ -5163,10 +5163,10 @@
         <v>45604</v>
       </c>
       <c r="B338" t="n">
-        <v>45.1880712754276</v>
+        <v>51.88736356985414</v>
       </c>
       <c r="C338" t="n">
-        <v>5.799305105104072</v>
+        <v>7.349782864654479</v>
       </c>
       <c r="D338" t="n">
         <v>0</v>
@@ -5177,10 +5177,10 @@
         <v>45611</v>
       </c>
       <c r="B339" t="n">
-        <v>45.68537045580661</v>
+        <v>52.61989778259277</v>
       </c>
       <c r="C339" t="n">
-        <v>6.308503318163335</v>
+        <v>7.9483838190794</v>
       </c>
       <c r="D339" t="n">
         <v>0</v>
@@ -5191,10 +5191,10 @@
         <v>45618</v>
       </c>
       <c r="B340" t="n">
-        <v>44.37750579488922</v>
+        <v>52.2617624106574</v>
       </c>
       <c r="C340" t="n">
-        <v>6.640320080355982</v>
+        <v>7.904276494695016</v>
       </c>
       <c r="D340" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>45625</v>
       </c>
       <c r="B341" t="n">
-        <v>45.21688043922439</v>
+        <v>52.29210220523964</v>
       </c>
       <c r="C341" t="n">
-        <v>6.824283008430005</v>
+        <v>7.898471673570287</v>
       </c>
       <c r="D341" t="n">
         <v>0</v>
@@ -5219,10 +5219,10 @@
         <v>45632</v>
       </c>
       <c r="B342" t="n">
-        <v>45.30999341815998</v>
+        <v>52.3277523852969</v>
       </c>
       <c r="C342" t="n">
-        <v>6.814099577849163</v>
+        <v>7.763011114070402</v>
       </c>
       <c r="D342" t="n">
         <v>0</v>
@@ -5233,10 +5233,10 @@
         <v>45639</v>
       </c>
       <c r="B343" t="n">
-        <v>45.09879480539997</v>
+        <v>51.88410228158761</v>
       </c>
       <c r="C343" t="n">
-        <v>6.456148550315373</v>
+        <v>7.840700982423213</v>
       </c>
       <c r="D343" t="n">
         <v>0</v>
@@ -5247,10 +5247,10 @@
         <v>45646</v>
       </c>
       <c r="B344" t="n">
-        <v>45.65835114724977</v>
+        <v>52.20397341730048</v>
       </c>
       <c r="C344" t="n">
-        <v>6.221702911616567</v>
+        <v>7.569849977265219</v>
       </c>
       <c r="D344" t="n">
         <v>0</v>
@@ -5261,10 +5261,10 @@
         <v>45653</v>
       </c>
       <c r="B345" t="n">
-        <v>46.16789928135336</v>
+        <v>53.11529595624506</v>
       </c>
       <c r="C345" t="n">
-        <v>6.537699708803837</v>
+        <v>7.601919077159247</v>
       </c>
       <c r="D345" t="n">
         <v>0</v>
@@ -5275,10 +5275,10 @@
         <v>45660</v>
       </c>
       <c r="B346" t="n">
-        <v>46.51158522195241</v>
+        <v>53.3709055077713</v>
       </c>
       <c r="C346" t="n">
-        <v>6.418607529306819</v>
+        <v>7.263009815165359</v>
       </c>
       <c r="D346" t="n">
         <v>0</v>
@@ -5289,10 +5289,10 @@
         <v>45667</v>
       </c>
       <c r="B347" t="n">
-        <v>46.80673221411575</v>
+        <v>53.85411300780155</v>
       </c>
       <c r="C347" t="n">
-        <v>6.796476700018724</v>
+        <v>7.93564072627007</v>
       </c>
       <c r="D347" t="n">
         <v>0</v>
@@ -5303,10 +5303,10 @@
         <v>45674</v>
       </c>
       <c r="B348" t="n">
-        <v>47.08634444970527</v>
+        <v>54.17038071492863</v>
       </c>
       <c r="C348" t="n">
-        <v>7.022280026271368</v>
+        <v>8.157371986211864</v>
       </c>
       <c r="D348" t="n">
         <v>0</v>
@@ -5317,10 +5317,10 @@
         <v>45681</v>
       </c>
       <c r="B349" t="n">
-        <v>46.97024008474158</v>
+        <v>54.55847586644948</v>
       </c>
       <c r="C349" t="n">
-        <v>7.332733272631271</v>
+        <v>8.870956254229421</v>
       </c>
       <c r="D349" t="n">
         <v>0</v>
@@ -5331,10 +5331,10 @@
         <v>45688</v>
       </c>
       <c r="B350" t="n">
-        <v>46.84267414025501</v>
+        <v>55.02590261335057</v>
       </c>
       <c r="C350" t="n">
-        <v>7.056383551274629</v>
+        <v>8.819420356362068</v>
       </c>
       <c r="D350" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>45695</v>
       </c>
       <c r="B351" t="n">
-        <v>44.0864004088917</v>
+        <v>52.15315194048398</v>
       </c>
       <c r="C351" t="n">
-        <v>3.883433804843915</v>
+        <v>6.338953806934802</v>
       </c>
       <c r="D351" t="n">
         <v>0</v>
@@ -5359,10 +5359,10 @@
         <v>45702</v>
       </c>
       <c r="B352" t="n">
-        <v>45.65904240014643</v>
+        <v>53.46596093207742</v>
       </c>
       <c r="C352" t="n">
-        <v>3.798549387476586</v>
+        <v>6.643159935362046</v>
       </c>
       <c r="D352" t="n">
         <v>0</v>
@@ -5373,10 +5373,10 @@
         <v>45709</v>
       </c>
       <c r="B353" t="n">
-        <v>45.20724113290286</v>
+        <v>52.89447107048375</v>
       </c>
       <c r="C353" t="n">
-        <v>4.0629345691876</v>
+        <v>6.955255443153994</v>
       </c>
       <c r="D353" t="n">
         <v>0</v>
@@ -5387,10 +5387,10 @@
         <v>45716</v>
       </c>
       <c r="B354" t="n">
-        <v>45.5557103118983</v>
+        <v>53.33366744558995</v>
       </c>
       <c r="C354" t="n">
-        <v>4.118221099741883</v>
+        <v>6.784482747287586</v>
       </c>
       <c r="D354" t="n">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>45723</v>
       </c>
       <c r="B355" t="n">
-        <v>46.39725072111735</v>
+        <v>53.83113533556141</v>
       </c>
       <c r="C355" t="n">
-        <v>5.163679819275261</v>
+        <v>7.337479341323396</v>
       </c>
       <c r="D355" t="n">
         <v>0</v>
@@ -5415,10 +5415,10 @@
         <v>45730</v>
       </c>
       <c r="B356" t="n">
-        <v>43.51450904577778</v>
+        <v>51.25430475657159</v>
       </c>
       <c r="C356" t="n">
-        <v>3.361636027416693</v>
+        <v>5.265763447914358</v>
       </c>
       <c r="D356" t="n">
         <v>0</v>
@@ -5429,10 +5429,10 @@
         <v>45737</v>
       </c>
       <c r="B357" t="n">
-        <v>43.50927884339063</v>
+        <v>51.33263124339421</v>
       </c>
       <c r="C357" t="n">
-        <v>2.493392771673796</v>
+        <v>3.143660103936284</v>
       </c>
       <c r="D357" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>45744</v>
       </c>
       <c r="B358" t="n">
-        <v>43.32333436547626</v>
+        <v>51.02869564002405</v>
       </c>
       <c r="C358" t="n">
-        <v>2.405192503104919</v>
+        <v>2.970876742637756</v>
       </c>
       <c r="D358" t="n">
         <v>0</v>
@@ -5457,10 +5457,10 @@
         <v>45751</v>
       </c>
       <c r="B359" t="n">
-        <v>43.1622318319336</v>
+        <v>50.54980984785546</v>
       </c>
       <c r="C359" t="n">
-        <v>2.46843681852255</v>
+        <v>2.724963655330992</v>
       </c>
       <c r="D359" t="n">
         <v>0</v>
@@ -5471,10 +5471,10 @@
         <v>45758</v>
       </c>
       <c r="B360" t="n">
-        <v>43.59165978162297</v>
+        <v>50.75853643960178</v>
       </c>
       <c r="C360" t="n">
-        <v>2.370059266809757</v>
+        <v>2.60649564785277</v>
       </c>
       <c r="D360" t="n">
         <v>0</v>
@@ -5485,10 +5485,10 @@
         <v>45765</v>
       </c>
       <c r="B361" t="n">
-        <v>43.60047800029241</v>
+        <v>50.88690708480269</v>
       </c>
       <c r="C361" t="n">
-        <v>2.394518877634715</v>
+        <v>2.661166898331323</v>
       </c>
       <c r="D361" t="n">
         <v>0</v>
@@ -5499,10 +5499,10 @@
         <v>45772</v>
       </c>
       <c r="B362" t="n">
-        <v>44.45331391748206</v>
+        <v>52.50779137753273</v>
       </c>
       <c r="C362" t="n">
-        <v>3.246813001924981</v>
+        <v>4.561415357497996</v>
       </c>
       <c r="D362" t="n">
         <v>0</v>
@@ -5513,10 +5513,10 @@
         <v>45779</v>
       </c>
       <c r="B363" t="n">
-        <v>43.84229529162133</v>
+        <v>51.13670288209227</v>
       </c>
       <c r="C363" t="n">
-        <v>2.928099675013101</v>
+        <v>4.813119594008316</v>
       </c>
       <c r="D363" t="n">
         <v>0</v>
@@ -5527,10 +5527,10 @@
         <v>45786</v>
       </c>
       <c r="B364" t="n">
-        <v>44.17610587251868</v>
+        <v>51.74761315958425</v>
       </c>
       <c r="C364" t="n">
-        <v>3.093020031573915</v>
+        <v>5.436781541834323</v>
       </c>
       <c r="D364" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>45793</v>
       </c>
       <c r="B365" t="n">
-        <v>43.7975590493582</v>
+        <v>51.64632865639896</v>
       </c>
       <c r="C365" t="n">
-        <v>3.125466346476937</v>
+        <v>5.338234940785236</v>
       </c>
       <c r="D365" t="n">
         <v>0</v>
@@ -5555,10 +5555,10 @@
         <v>45800</v>
       </c>
       <c r="B366" t="n">
-        <v>44.16957892346554</v>
+        <v>51.9586509149517</v>
       </c>
       <c r="C366" t="n">
-        <v>3.81001755030097</v>
+        <v>6.464055653876669</v>
       </c>
       <c r="D366" t="n">
         <v>0</v>
@@ -5569,10 +5569,10 @@
         <v>45807</v>
       </c>
       <c r="B367" t="n">
-        <v>43.82707699438947</v>
+        <v>52.45344438555446</v>
       </c>
       <c r="C367" t="n">
-        <v>3.671954576122159</v>
+        <v>5.806619721633719</v>
       </c>
       <c r="D367" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>45814</v>
       </c>
       <c r="B368" t="n">
-        <v>44.68036439166068</v>
+        <v>53.53554634874545</v>
       </c>
       <c r="C368" t="n">
-        <v>4.080954505722439</v>
+        <v>6.550882288756909</v>
       </c>
       <c r="D368" t="n">
         <v>0</v>
@@ -5597,10 +5597,10 @@
         <v>45821</v>
       </c>
       <c r="B369" t="n">
-        <v>44.75337952343097</v>
+        <v>53.5236526789316</v>
       </c>
       <c r="C369" t="n">
-        <v>4.091616050798228</v>
+        <v>6.331224698946714</v>
       </c>
       <c r="D369" t="n">
         <v>0</v>
@@ -5611,10 +5611,10 @@
         <v>45828</v>
       </c>
       <c r="B370" t="n">
-        <v>44.42848435065968</v>
+        <v>53.15885434167122</v>
       </c>
       <c r="C370" t="n">
-        <v>4.401705305948503</v>
+        <v>6.431388279075655</v>
       </c>
       <c r="D370" t="n">
         <v>0</v>
@@ -5625,10 +5625,10 @@
         <v>45835</v>
       </c>
       <c r="B371" t="n">
-        <v>45.23406423286551</v>
+        <v>53.62747150195033</v>
       </c>
       <c r="C371" t="n">
-        <v>4.401641055978383</v>
+        <v>6.281935344133759</v>
       </c>
       <c r="D371" t="n">
         <v>0</v>
@@ -5639,10 +5639,10 @@
         <v>45842</v>
       </c>
       <c r="B372" t="n">
-        <v>45.47075355622832</v>
+        <v>53.71444814053199</v>
       </c>
       <c r="C372" t="n">
-        <v>4.192527602574073</v>
+        <v>6.261897710878593</v>
       </c>
       <c r="D372" t="n">
         <v>0</v>
@@ -5653,10 +5653,10 @@
         <v>45849</v>
       </c>
       <c r="B373" t="n">
-        <v>45.45077878185491</v>
+        <v>53.53461176042469</v>
       </c>
       <c r="C373" t="n">
-        <v>4.230686161709111</v>
+        <v>6.323624989289292</v>
       </c>
       <c r="D373" t="n">
         <v>0</v>
